--- a/convert/coudfarms/Input/15 2026.xlsx
+++ b/convert/coudfarms/Input/15 2026.xlsx
@@ -189,11 +189,6 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="BB0000"/>
-      </patternFill>
-    </fill>
-    <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
@@ -693,11 +688,11 @@
       <alignment wrapText="true" horizontal="right" vertical="center"/>
       <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="22" borderId="16" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="1" fontId="6" fillId="22" borderId="17" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment wrapText="true" horizontal="right" vertical="center"/>
       <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="23" borderId="17" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="2" fontId="6" fillId="23" borderId="16" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment wrapText="true" horizontal="right" vertical="center"/>
       <protection hidden="false" locked="true"/>
     </xf>
@@ -705,91 +700,87 @@
       <alignment wrapText="true" horizontal="right" vertical="center"/>
       <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="25" borderId="16" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="2" fontId="6" fillId="25" borderId="17" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment wrapText="true" horizontal="right" vertical="center"/>
       <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="26" borderId="17" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="3" fontId="6" fillId="26" borderId="16" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment wrapText="true" horizontal="right" vertical="center"/>
       <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="27" borderId="16" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="3" fontId="6" fillId="27" borderId="17" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment wrapText="true" horizontal="right" vertical="center"/>
       <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="28" borderId="17" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="3" fontId="6" fillId="28" borderId="16" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment wrapText="true" horizontal="right" vertical="center"/>
       <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="29" borderId="16" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="3" fontId="7" fillId="29" borderId="16" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment wrapText="true" horizontal="right" vertical="center"/>
       <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="30" borderId="16" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="4" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment wrapText="true" horizontal="left" vertical="top"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="31" borderId="16" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment wrapText="true" horizontal="right" vertical="center"/>
       <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="4" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment wrapText="true" horizontal="left" vertical="top"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="32" borderId="16" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="2" fontId="6" fillId="32" borderId="17" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment wrapText="true" horizontal="right" vertical="center"/>
       <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="33" borderId="17" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="3" fontId="7" fillId="33" borderId="17" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment wrapText="true" horizontal="right" vertical="center"/>
       <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="34" borderId="17" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="2" fontId="7" fillId="34" borderId="16" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment wrapText="true" horizontal="right" vertical="center"/>
       <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="35" borderId="16" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="2" fontId="7" fillId="35" borderId="17" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment wrapText="true" horizontal="right" vertical="center"/>
       <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="36" borderId="17" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="1" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment wrapText="true" horizontal="left" vertical="center"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="37" borderId="18" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment wrapText="true" horizontal="left" vertical="center"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="38" borderId="19" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment wrapText="true" horizontal="right" vertical="center"/>
       <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="37" borderId="1" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="39" borderId="18" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment wrapText="true" horizontal="left" vertical="center"/>
       <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="38" borderId="18" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="20" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment wrapText="true" horizontal="right" vertical="center"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="41" borderId="21" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment wrapText="true" horizontal="left" vertical="center"/>
       <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="39" borderId="19" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="4" fontId="5" fillId="42" borderId="19" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment wrapText="true" horizontal="right" vertical="center"/>
       <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="18" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment wrapText="true" horizontal="left" vertical="center"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="41" borderId="20" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment wrapText="true" horizontal="right" vertical="center"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="21" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment wrapText="true" horizontal="left" vertical="center"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="43" borderId="19" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment wrapText="true" horizontal="right" vertical="center"/>
-      <protection hidden="false" locked="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="44" borderId="4" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="4" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment wrapText="true"/>
       <protection hidden="false" locked="false"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="45" borderId="1" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="44" borderId="1" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment wrapText="true" horizontal="right" vertical="bottom"/>
       <protection hidden="false" locked="true"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="46" borderId="1" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="45" borderId="1" xfId="0" applyAlignment="1" applyProtection="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment wrapText="true" horizontal="right" vertical="center"/>
       <protection hidden="false" locked="true"/>
     </xf>
@@ -816,7 +807,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="271218280" name="Picture">
+        <xdr:cNvPr id="350219211" name="Picture">
 </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
@@ -1074,7 +1065,7 @@
       <c r="A6" s="3" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Beregningstid 12.04.2026 07.58</t>
+            <t xml:space="preserve">Beregningstid 12.04.2026 19.53</t>
           </r>
         </is>
       </c>
@@ -1372,23 +1363,23 @@
       </c>
       <c r="G11" s="20" t="inlineStr"/>
       <c r="H11" s="20" t="inlineStr"/>
-      <c r="I11" s="21" t="n">
-        <v>84.0</v>
-      </c>
-      <c r="J11" s="21" t="inlineStr"/>
-      <c r="K11" s="21" t="inlineStr"/>
+      <c r="I11" s="20" t="n">
+        <v>90.0</v>
+      </c>
+      <c r="J11" s="20" t="inlineStr"/>
+      <c r="K11" s="20" t="inlineStr"/>
       <c r="L11" s="20" t="n">
-        <v>88.0</v>
+        <v>90.0</v>
       </c>
       <c r="M11" s="20" t="inlineStr"/>
       <c r="N11" s="20" t="inlineStr"/>
       <c r="O11" s="20" t="inlineStr"/>
       <c r="P11" s="20" t="n">
-        <v>-7.0</v>
+        <v>-1.0</v>
       </c>
       <c r="Q11" s="20" t="inlineStr"/>
       <c r="R11" s="20" t="n">
-        <v>89.0</v>
+        <v>90.0</v>
       </c>
       <c r="S11" s="20" t="inlineStr"/>
       <c r="T11" s="20" t="inlineStr"/>
@@ -1398,17 +1389,17 @@
       <c r="V11" s="20" t="inlineStr"/>
       <c r="W11" s="20" t="inlineStr"/>
       <c r="X11" s="20" t="n">
-        <v>-19.0</v>
+        <v>-13.0</v>
       </c>
       <c r="Y11" s="20" t="inlineStr"/>
       <c r="Z11" s="20" t="inlineStr"/>
       <c r="AA11" s="20" t="inlineStr"/>
       <c r="AB11" s="20" t="inlineStr"/>
-      <c r="AC11" s="22" t="n">
-        <v>89.0</v>
-      </c>
-      <c r="AD11" s="22" t="inlineStr"/>
-      <c r="AE11" s="22" t="inlineStr"/>
+      <c r="AC11" s="21" t="n">
+        <v>90.0</v>
+      </c>
+      <c r="AD11" s="21" t="inlineStr"/>
+      <c r="AE11" s="21" t="inlineStr"/>
     </row>
     <row r="12" customHeight="1" ht="15">
       <c r="A12" s="19" t="inlineStr">
@@ -1453,11 +1444,11 @@
       <c r="Z12" s="20" t="inlineStr"/>
       <c r="AA12" s="20" t="inlineStr"/>
       <c r="AB12" s="20" t="inlineStr"/>
-      <c r="AC12" s="22" t="n">
+      <c r="AC12" s="21" t="n">
         <v>31.0</v>
       </c>
-      <c r="AD12" s="22" t="inlineStr"/>
-      <c r="AE12" s="22" t="inlineStr"/>
+      <c r="AD12" s="21" t="inlineStr"/>
+      <c r="AE12" s="21" t="inlineStr"/>
     </row>
     <row r="13" customHeight="1" ht="15">
       <c r="A13" s="19" t="inlineStr">
@@ -1475,12 +1466,12 @@
       <c r="G13" s="20" t="inlineStr"/>
       <c r="H13" s="20" t="inlineStr"/>
       <c r="I13" s="20" t="n">
-        <v>56.0</v>
+        <v>61.0</v>
       </c>
       <c r="J13" s="20" t="inlineStr"/>
       <c r="K13" s="20" t="inlineStr"/>
       <c r="L13" s="20" t="n">
-        <v>58.0</v>
+        <v>59.0</v>
       </c>
       <c r="M13" s="20" t="inlineStr"/>
       <c r="N13" s="20" t="inlineStr"/>
@@ -1493,7 +1484,7 @@
       <c r="S13" s="20" t="inlineStr"/>
       <c r="T13" s="20" t="inlineStr"/>
       <c r="U13" s="20" t="n">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
       <c r="V13" s="20" t="inlineStr"/>
       <c r="W13" s="20" t="inlineStr"/>
@@ -1502,11 +1493,11 @@
       <c r="Z13" s="20" t="inlineStr"/>
       <c r="AA13" s="20" t="inlineStr"/>
       <c r="AB13" s="20" t="inlineStr"/>
-      <c r="AC13" s="22" t="n">
+      <c r="AC13" s="21" t="n">
         <v>55.0</v>
       </c>
-      <c r="AD13" s="22" t="inlineStr"/>
-      <c r="AE13" s="22" t="inlineStr"/>
+      <c r="AD13" s="21" t="inlineStr"/>
+      <c r="AE13" s="21" t="inlineStr"/>
     </row>
     <row r="14" customHeight="1" ht="15">
       <c r="A14" s="19" t="inlineStr">
@@ -1524,7 +1515,7 @@
       <c r="G14" s="20" t="inlineStr"/>
       <c r="H14" s="20" t="inlineStr"/>
       <c r="I14" s="20" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="J14" s="20" t="inlineStr"/>
       <c r="K14" s="20" t="inlineStr"/>
@@ -1551,11 +1542,11 @@
       <c r="Z14" s="20" t="inlineStr"/>
       <c r="AA14" s="20" t="inlineStr"/>
       <c r="AB14" s="20" t="inlineStr"/>
-      <c r="AC14" s="22" t="n">
+      <c r="AC14" s="21" t="n">
         <v>4.0</v>
       </c>
-      <c r="AD14" s="22" t="inlineStr"/>
-      <c r="AE14" s="22" t="inlineStr"/>
+      <c r="AD14" s="21" t="inlineStr"/>
+      <c r="AE14" s="21" t="inlineStr"/>
     </row>
     <row r="15" customHeight="1" ht="15">
       <c r="A15" s="19" t="inlineStr">
@@ -1569,48 +1560,48 @@
       <c r="C15" s="19" t="inlineStr"/>
       <c r="D15" s="19" t="inlineStr"/>
       <c r="E15" s="19" t="inlineStr"/>
-      <c r="F15" s="23" t="n">
+      <c r="F15" s="22" t="n">
         <v>5.5</v>
       </c>
-      <c r="G15" s="23" t="inlineStr"/>
-      <c r="H15" s="23" t="inlineStr"/>
-      <c r="I15" s="24" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="J15" s="24" t="inlineStr"/>
-      <c r="K15" s="24" t="inlineStr"/>
-      <c r="L15" s="23" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="M15" s="23" t="inlineStr"/>
-      <c r="N15" s="23" t="inlineStr"/>
-      <c r="O15" s="23" t="inlineStr"/>
-      <c r="P15" s="23" t="n">
-        <v>-0.11756373937677012</v>
-      </c>
-      <c r="Q15" s="23" t="inlineStr"/>
-      <c r="R15" s="23" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="S15" s="23" t="inlineStr"/>
-      <c r="T15" s="23" t="inlineStr"/>
-      <c r="U15" s="24" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="V15" s="24" t="inlineStr"/>
-      <c r="W15" s="24" t="inlineStr"/>
-      <c r="X15" s="23" t="n">
-        <v>-1.0665024630541868</v>
-      </c>
-      <c r="Y15" s="23" t="inlineStr"/>
-      <c r="Z15" s="23" t="inlineStr"/>
-      <c r="AA15" s="23" t="inlineStr"/>
-      <c r="AB15" s="23" t="inlineStr"/>
-      <c r="AC15" s="25" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AD15" s="25" t="inlineStr"/>
-      <c r="AE15" s="25" t="inlineStr"/>
+      <c r="G15" s="22" t="inlineStr"/>
+      <c r="H15" s="22" t="inlineStr"/>
+      <c r="I15" s="23" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="J15" s="23" t="inlineStr"/>
+      <c r="K15" s="23" t="inlineStr"/>
+      <c r="L15" s="22" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="M15" s="22" t="inlineStr"/>
+      <c r="N15" s="22" t="inlineStr"/>
+      <c r="O15" s="22" t="inlineStr"/>
+      <c r="P15" s="22" t="n">
+        <v>0.07103064066852394</v>
+      </c>
+      <c r="Q15" s="22" t="inlineStr"/>
+      <c r="R15" s="22" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="S15" s="22" t="inlineStr"/>
+      <c r="T15" s="22" t="inlineStr"/>
+      <c r="U15" s="23" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="V15" s="23" t="inlineStr"/>
+      <c r="W15" s="23" t="inlineStr"/>
+      <c r="X15" s="22" t="n">
+        <v>-1.0150665732305537</v>
+      </c>
+      <c r="Y15" s="22" t="inlineStr"/>
+      <c r="Z15" s="22" t="inlineStr"/>
+      <c r="AA15" s="22" t="inlineStr"/>
+      <c r="AB15" s="22" t="inlineStr"/>
+      <c r="AC15" s="24" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="AD15" s="24" t="inlineStr"/>
+      <c r="AE15" s="24" t="inlineStr"/>
     </row>
     <row r="16" customHeight="1" ht="15">
       <c r="A16" s="19" t="inlineStr">
@@ -1624,48 +1615,48 @@
       <c r="C16" s="19" t="inlineStr"/>
       <c r="D16" s="19" t="inlineStr"/>
       <c r="E16" s="19" t="inlineStr"/>
-      <c r="F16" s="26" t="n">
+      <c r="F16" s="25" t="n">
         <v>7.0</v>
       </c>
-      <c r="G16" s="26" t="inlineStr"/>
-      <c r="H16" s="26" t="inlineStr"/>
-      <c r="I16" s="26" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J16" s="26" t="inlineStr"/>
-      <c r="K16" s="26" t="inlineStr"/>
-      <c r="L16" s="26" t="n">
+      <c r="G16" s="25" t="inlineStr"/>
+      <c r="H16" s="25" t="inlineStr"/>
+      <c r="I16" s="25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J16" s="25" t="inlineStr"/>
+      <c r="K16" s="25" t="inlineStr"/>
+      <c r="L16" s="25" t="n">
         <v>6.3</v>
       </c>
-      <c r="M16" s="26" t="inlineStr"/>
-      <c r="N16" s="26" t="inlineStr"/>
-      <c r="O16" s="26" t="inlineStr"/>
-      <c r="P16" s="26" t="n">
-        <v>-0.7456896551724137</v>
-      </c>
-      <c r="Q16" s="26" t="inlineStr"/>
-      <c r="R16" s="26" t="n">
+      <c r="M16" s="25" t="inlineStr"/>
+      <c r="N16" s="25" t="inlineStr"/>
+      <c r="O16" s="25" t="inlineStr"/>
+      <c r="P16" s="25" t="n">
+        <v>-0.7299578059071727</v>
+      </c>
+      <c r="Q16" s="25" t="inlineStr"/>
+      <c r="R16" s="25" t="n">
         <v>6.6</v>
       </c>
-      <c r="S16" s="26" t="inlineStr"/>
-      <c r="T16" s="26" t="inlineStr"/>
-      <c r="U16" s="26" t="n">
+      <c r="S16" s="25" t="inlineStr"/>
+      <c r="T16" s="25" t="inlineStr"/>
+      <c r="U16" s="25" t="n">
         <v>6.5</v>
       </c>
-      <c r="V16" s="26" t="inlineStr"/>
-      <c r="W16" s="26" t="inlineStr"/>
-      <c r="X16" s="26" t="n">
-        <v>-0.46440677966101696</v>
-      </c>
-      <c r="Y16" s="26" t="inlineStr"/>
-      <c r="Z16" s="26" t="inlineStr"/>
-      <c r="AA16" s="26" t="inlineStr"/>
-      <c r="AB16" s="26" t="inlineStr"/>
-      <c r="AC16" s="27" t="n">
+      <c r="V16" s="25" t="inlineStr"/>
+      <c r="W16" s="25" t="inlineStr"/>
+      <c r="X16" s="25" t="n">
+        <v>-0.46179775280898916</v>
+      </c>
+      <c r="Y16" s="25" t="inlineStr"/>
+      <c r="Z16" s="25" t="inlineStr"/>
+      <c r="AA16" s="25" t="inlineStr"/>
+      <c r="AB16" s="25" t="inlineStr"/>
+      <c r="AC16" s="26" t="n">
         <v>6.5</v>
       </c>
-      <c r="AD16" s="27" t="inlineStr"/>
-      <c r="AE16" s="27" t="inlineStr"/>
+      <c r="AD16" s="26" t="inlineStr"/>
+      <c r="AE16" s="26" t="inlineStr"/>
     </row>
     <row r="17" customHeight="1" ht="15">
       <c r="A17" s="19" t="inlineStr">
@@ -1679,11 +1670,11 @@
       <c r="C17" s="19" t="inlineStr"/>
       <c r="D17" s="19" t="inlineStr"/>
       <c r="E17" s="19" t="inlineStr"/>
-      <c r="F17" s="26" t="n"/>
-      <c r="G17" s="26" t="inlineStr"/>
-      <c r="H17" s="26" t="inlineStr"/>
+      <c r="F17" s="25" t="n"/>
+      <c r="G17" s="25" t="inlineStr"/>
+      <c r="H17" s="25" t="inlineStr"/>
       <c r="I17" s="20" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="J17" s="20" t="inlineStr"/>
       <c r="K17" s="20" t="inlineStr"/>
@@ -1693,10 +1684,10 @@
       <c r="M17" s="20" t="inlineStr"/>
       <c r="N17" s="20" t="inlineStr"/>
       <c r="O17" s="20" t="inlineStr"/>
-      <c r="P17" s="26" t="n"/>
-      <c r="Q17" s="26" t="inlineStr"/>
+      <c r="P17" s="25" t="n"/>
+      <c r="Q17" s="25" t="inlineStr"/>
       <c r="R17" s="20" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="S17" s="20" t="inlineStr"/>
       <c r="T17" s="20" t="inlineStr"/>
@@ -1705,16 +1696,16 @@
       </c>
       <c r="V17" s="20" t="inlineStr"/>
       <c r="W17" s="20" t="inlineStr"/>
-      <c r="X17" s="26" t="n"/>
-      <c r="Y17" s="26" t="inlineStr"/>
-      <c r="Z17" s="26" t="inlineStr"/>
-      <c r="AA17" s="26" t="inlineStr"/>
-      <c r="AB17" s="26" t="inlineStr"/>
-      <c r="AC17" s="22" t="n">
+      <c r="X17" s="25" t="n"/>
+      <c r="Y17" s="25" t="inlineStr"/>
+      <c r="Z17" s="25" t="inlineStr"/>
+      <c r="AA17" s="25" t="inlineStr"/>
+      <c r="AB17" s="25" t="inlineStr"/>
+      <c r="AC17" s="21" t="n">
         <v>9.0</v>
       </c>
-      <c r="AD17" s="22" t="inlineStr"/>
-      <c r="AE17" s="22" t="inlineStr"/>
+      <c r="AD17" s="21" t="inlineStr"/>
+      <c r="AE17" s="21" t="inlineStr"/>
     </row>
     <row r="18" customHeight="1" ht="15">
       <c r="A18" s="19" t="inlineStr">
@@ -1728,48 +1719,48 @@
       <c r="C18" s="19" t="inlineStr"/>
       <c r="D18" s="19" t="inlineStr"/>
       <c r="E18" s="19" t="inlineStr"/>
-      <c r="F18" s="26" t="n">
+      <c r="F18" s="25" t="n">
         <v>95.0</v>
       </c>
-      <c r="G18" s="26" t="inlineStr"/>
-      <c r="H18" s="26" t="inlineStr"/>
-      <c r="I18" s="28" t="n">
+      <c r="G18" s="25" t="inlineStr"/>
+      <c r="H18" s="25" t="inlineStr"/>
+      <c r="I18" s="27" t="n">
         <v>96.7</v>
       </c>
-      <c r="J18" s="28" t="inlineStr"/>
-      <c r="K18" s="28" t="inlineStr"/>
-      <c r="L18" s="28" t="n">
+      <c r="J18" s="27" t="inlineStr"/>
+      <c r="K18" s="27" t="inlineStr"/>
+      <c r="L18" s="27" t="n">
         <v>96.4</v>
       </c>
-      <c r="M18" s="28" t="inlineStr"/>
-      <c r="N18" s="28" t="inlineStr"/>
-      <c r="O18" s="28" t="inlineStr"/>
-      <c r="P18" s="26" t="n">
+      <c r="M18" s="27" t="inlineStr"/>
+      <c r="N18" s="27" t="inlineStr"/>
+      <c r="O18" s="27" t="inlineStr"/>
+      <c r="P18" s="25" t="n">
         <v>1.3585434173669455</v>
       </c>
-      <c r="Q18" s="26" t="inlineStr"/>
-      <c r="R18" s="28" t="n">
+      <c r="Q18" s="25" t="inlineStr"/>
+      <c r="R18" s="27" t="n">
         <v>96.8</v>
       </c>
-      <c r="S18" s="28" t="inlineStr"/>
-      <c r="T18" s="28" t="inlineStr"/>
-      <c r="U18" s="26" t="n">
+      <c r="S18" s="27" t="inlineStr"/>
+      <c r="T18" s="27" t="inlineStr"/>
+      <c r="U18" s="25" t="n">
         <v>95.9</v>
       </c>
-      <c r="V18" s="26" t="inlineStr"/>
-      <c r="W18" s="26" t="inlineStr"/>
-      <c r="X18" s="26" t="n">
+      <c r="V18" s="25" t="inlineStr"/>
+      <c r="W18" s="25" t="inlineStr"/>
+      <c r="X18" s="25" t="n">
         <v>0.941217634709588</v>
       </c>
-      <c r="Y18" s="26" t="inlineStr"/>
-      <c r="Z18" s="26" t="inlineStr"/>
-      <c r="AA18" s="26" t="inlineStr"/>
-      <c r="AB18" s="26" t="inlineStr"/>
-      <c r="AC18" s="27" t="n">
+      <c r="Y18" s="25" t="inlineStr"/>
+      <c r="Z18" s="25" t="inlineStr"/>
+      <c r="AA18" s="25" t="inlineStr"/>
+      <c r="AB18" s="25" t="inlineStr"/>
+      <c r="AC18" s="26" t="n">
         <v>96.0</v>
       </c>
-      <c r="AD18" s="27" t="inlineStr"/>
-      <c r="AE18" s="27" t="inlineStr"/>
+      <c r="AD18" s="26" t="inlineStr"/>
+      <c r="AE18" s="26" t="inlineStr"/>
     </row>
     <row r="19" customHeight="1" ht="15">
       <c r="A19" s="19" t="inlineStr">
@@ -1783,48 +1774,48 @@
       <c r="C19" s="19" t="inlineStr"/>
       <c r="D19" s="19" t="inlineStr"/>
       <c r="E19" s="19" t="inlineStr"/>
-      <c r="F19" s="26" t="n">
+      <c r="F19" s="25" t="n">
         <v>95.0</v>
       </c>
-      <c r="G19" s="26" t="inlineStr"/>
-      <c r="H19" s="26" t="inlineStr"/>
-      <c r="I19" s="26" t="n">
+      <c r="G19" s="25" t="inlineStr"/>
+      <c r="H19" s="25" t="inlineStr"/>
+      <c r="I19" s="25" t="n">
         <v>94.4</v>
       </c>
-      <c r="J19" s="26" t="inlineStr"/>
-      <c r="K19" s="26" t="inlineStr"/>
-      <c r="L19" s="26" t="n">
+      <c r="J19" s="25" t="inlineStr"/>
+      <c r="K19" s="25" t="inlineStr"/>
+      <c r="L19" s="25" t="n">
         <v>93.5</v>
       </c>
-      <c r="M19" s="26" t="inlineStr"/>
-      <c r="N19" s="26" t="inlineStr"/>
-      <c r="O19" s="26" t="inlineStr"/>
-      <c r="P19" s="26" t="n">
+      <c r="M19" s="25" t="inlineStr"/>
+      <c r="N19" s="25" t="inlineStr"/>
+      <c r="O19" s="25" t="inlineStr"/>
+      <c r="P19" s="25" t="n">
         <v>-1.4788732394366235</v>
       </c>
-      <c r="Q19" s="26" t="inlineStr"/>
-      <c r="R19" s="26" t="n">
+      <c r="Q19" s="25" t="inlineStr"/>
+      <c r="R19" s="25" t="n">
         <v>93.5</v>
       </c>
-      <c r="S19" s="26" t="inlineStr"/>
-      <c r="T19" s="26" t="inlineStr"/>
-      <c r="U19" s="26" t="n">
+      <c r="S19" s="25" t="inlineStr"/>
+      <c r="T19" s="25" t="inlineStr"/>
+      <c r="U19" s="25" t="n">
         <v>93.3</v>
       </c>
-      <c r="V19" s="26" t="inlineStr"/>
-      <c r="W19" s="26" t="inlineStr"/>
-      <c r="X19" s="26" t="n">
+      <c r="V19" s="25" t="inlineStr"/>
+      <c r="W19" s="25" t="inlineStr"/>
+      <c r="X19" s="25" t="n">
         <v>-1.6619915848527285</v>
       </c>
-      <c r="Y19" s="26" t="inlineStr"/>
-      <c r="Z19" s="26" t="inlineStr"/>
-      <c r="AA19" s="26" t="inlineStr"/>
-      <c r="AB19" s="26" t="inlineStr"/>
-      <c r="AC19" s="27" t="n">
+      <c r="Y19" s="25" t="inlineStr"/>
+      <c r="Z19" s="25" t="inlineStr"/>
+      <c r="AA19" s="25" t="inlineStr"/>
+      <c r="AB19" s="25" t="inlineStr"/>
+      <c r="AC19" s="26" t="n">
         <v>93.8</v>
       </c>
-      <c r="AD19" s="27" t="inlineStr"/>
-      <c r="AE19" s="27" t="inlineStr"/>
+      <c r="AD19" s="26" t="inlineStr"/>
+      <c r="AE19" s="26" t="inlineStr"/>
     </row>
     <row r="20" customHeight="1" ht="15">
       <c r="A20" s="19" t="inlineStr">
@@ -1838,48 +1829,48 @@
       <c r="C20" s="19" t="inlineStr"/>
       <c r="D20" s="19" t="inlineStr"/>
       <c r="E20" s="19" t="inlineStr"/>
-      <c r="F20" s="26" t="n">
+      <c r="F20" s="25" t="n">
         <v>92.0</v>
       </c>
-      <c r="G20" s="26" t="inlineStr"/>
-      <c r="H20" s="26" t="inlineStr"/>
-      <c r="I20" s="29" t="n">
+      <c r="G20" s="25" t="inlineStr"/>
+      <c r="H20" s="25" t="inlineStr"/>
+      <c r="I20" s="28" t="n">
         <v>86.5</v>
       </c>
-      <c r="J20" s="29" t="inlineStr"/>
-      <c r="K20" s="29" t="inlineStr"/>
-      <c r="L20" s="26" t="n">
+      <c r="J20" s="28" t="inlineStr"/>
+      <c r="K20" s="28" t="inlineStr"/>
+      <c r="L20" s="25" t="n">
         <v>90.7</v>
       </c>
-      <c r="M20" s="26" t="inlineStr"/>
-      <c r="N20" s="26" t="inlineStr"/>
-      <c r="O20" s="26" t="inlineStr"/>
-      <c r="P20" s="26" t="n">
+      <c r="M20" s="25" t="inlineStr"/>
+      <c r="N20" s="25" t="inlineStr"/>
+      <c r="O20" s="25" t="inlineStr"/>
+      <c r="P20" s="25" t="n">
         <v>-1.3484419263456147</v>
       </c>
-      <c r="Q20" s="26" t="inlineStr"/>
-      <c r="R20" s="26" t="n">
+      <c r="Q20" s="25" t="inlineStr"/>
+      <c r="R20" s="25" t="n">
         <v>91.8</v>
       </c>
-      <c r="S20" s="26" t="inlineStr"/>
-      <c r="T20" s="26" t="inlineStr"/>
-      <c r="U20" s="26" t="n">
+      <c r="S20" s="25" t="inlineStr"/>
+      <c r="T20" s="25" t="inlineStr"/>
+      <c r="U20" s="25" t="n">
         <v>91.5</v>
       </c>
-      <c r="V20" s="26" t="inlineStr"/>
-      <c r="W20" s="26" t="inlineStr"/>
-      <c r="X20" s="26" t="n">
+      <c r="V20" s="25" t="inlineStr"/>
+      <c r="W20" s="25" t="inlineStr"/>
+      <c r="X20" s="25" t="n">
         <v>-0.5374387683694835</v>
       </c>
-      <c r="Y20" s="26" t="inlineStr"/>
-      <c r="Z20" s="26" t="inlineStr"/>
-      <c r="AA20" s="26" t="inlineStr"/>
-      <c r="AB20" s="26" t="inlineStr"/>
-      <c r="AC20" s="27" t="n">
+      <c r="Y20" s="25" t="inlineStr"/>
+      <c r="Z20" s="25" t="inlineStr"/>
+      <c r="AA20" s="25" t="inlineStr"/>
+      <c r="AB20" s="25" t="inlineStr"/>
+      <c r="AC20" s="26" t="n">
         <v>92.2</v>
       </c>
-      <c r="AD20" s="27" t="inlineStr"/>
-      <c r="AE20" s="27" t="inlineStr"/>
+      <c r="AD20" s="26" t="inlineStr"/>
+      <c r="AE20" s="26" t="inlineStr"/>
     </row>
     <row r="21" customHeight="1" ht="15">
       <c r="A21" s="19" t="inlineStr">
@@ -1930,44 +1921,44 @@
       <c r="Z21" s="20" t="inlineStr"/>
       <c r="AA21" s="20" t="inlineStr"/>
       <c r="AB21" s="20" t="inlineStr"/>
-      <c r="AC21" s="22" t="n">
+      <c r="AC21" s="21" t="n">
         <v>5.0</v>
       </c>
-      <c r="AD21" s="22" t="inlineStr"/>
-      <c r="AE21" s="22" t="inlineStr"/>
+      <c r="AD21" s="21" t="inlineStr"/>
+      <c r="AE21" s="21" t="inlineStr"/>
     </row>
     <row r="22" customHeight="1" ht="2">
-      <c r="A22" s="30" t="inlineStr"/>
-      <c r="B22" s="30" t="inlineStr"/>
-      <c r="C22" s="30" t="inlineStr"/>
-      <c r="D22" s="30" t="inlineStr"/>
-      <c r="E22" s="30" t="inlineStr"/>
-      <c r="F22" s="30" t="inlineStr"/>
-      <c r="G22" s="30" t="inlineStr"/>
-      <c r="H22" s="30" t="inlineStr"/>
-      <c r="I22" s="30" t="inlineStr"/>
-      <c r="J22" s="30" t="inlineStr"/>
-      <c r="K22" s="30" t="inlineStr"/>
-      <c r="L22" s="30" t="inlineStr"/>
-      <c r="M22" s="30" t="inlineStr"/>
-      <c r="N22" s="30" t="inlineStr"/>
-      <c r="O22" s="30" t="inlineStr"/>
-      <c r="P22" s="30" t="inlineStr"/>
-      <c r="Q22" s="30" t="inlineStr"/>
-      <c r="R22" s="30" t="inlineStr"/>
-      <c r="S22" s="30" t="inlineStr"/>
-      <c r="T22" s="30" t="inlineStr"/>
-      <c r="U22" s="30" t="inlineStr"/>
-      <c r="V22" s="30" t="inlineStr"/>
-      <c r="W22" s="30" t="inlineStr"/>
-      <c r="X22" s="30" t="inlineStr"/>
-      <c r="Y22" s="30" t="inlineStr"/>
-      <c r="Z22" s="30" t="inlineStr"/>
-      <c r="AA22" s="30" t="inlineStr"/>
-      <c r="AB22" s="30" t="inlineStr"/>
-      <c r="AC22" s="30" t="inlineStr"/>
-      <c r="AD22" s="30" t="inlineStr"/>
-      <c r="AE22" s="30" t="inlineStr"/>
+      <c r="A22" s="29" t="inlineStr"/>
+      <c r="B22" s="29" t="inlineStr"/>
+      <c r="C22" s="29" t="inlineStr"/>
+      <c r="D22" s="29" t="inlineStr"/>
+      <c r="E22" s="29" t="inlineStr"/>
+      <c r="F22" s="29" t="inlineStr"/>
+      <c r="G22" s="29" t="inlineStr"/>
+      <c r="H22" s="29" t="inlineStr"/>
+      <c r="I22" s="29" t="inlineStr"/>
+      <c r="J22" s="29" t="inlineStr"/>
+      <c r="K22" s="29" t="inlineStr"/>
+      <c r="L22" s="29" t="inlineStr"/>
+      <c r="M22" s="29" t="inlineStr"/>
+      <c r="N22" s="29" t="inlineStr"/>
+      <c r="O22" s="29" t="inlineStr"/>
+      <c r="P22" s="29" t="inlineStr"/>
+      <c r="Q22" s="29" t="inlineStr"/>
+      <c r="R22" s="29" t="inlineStr"/>
+      <c r="S22" s="29" t="inlineStr"/>
+      <c r="T22" s="29" t="inlineStr"/>
+      <c r="U22" s="29" t="inlineStr"/>
+      <c r="V22" s="29" t="inlineStr"/>
+      <c r="W22" s="29" t="inlineStr"/>
+      <c r="X22" s="29" t="inlineStr"/>
+      <c r="Y22" s="29" t="inlineStr"/>
+      <c r="Z22" s="29" t="inlineStr"/>
+      <c r="AA22" s="29" t="inlineStr"/>
+      <c r="AB22" s="29" t="inlineStr"/>
+      <c r="AC22" s="29" t="inlineStr"/>
+      <c r="AD22" s="29" t="inlineStr"/>
+      <c r="AE22" s="29" t="inlineStr"/>
     </row>
     <row r="23" customHeight="1" ht="21">
       <c r="A23" s="4" t="inlineStr">
@@ -2232,11 +2223,11 @@
       </c>
       <c r="G27" s="20" t="inlineStr"/>
       <c r="H27" s="20" t="inlineStr"/>
-      <c r="I27" s="31" t="n">
+      <c r="I27" s="30" t="n">
         <v>84.0</v>
       </c>
-      <c r="J27" s="31" t="inlineStr"/>
-      <c r="K27" s="31" t="inlineStr"/>
+      <c r="J27" s="30" t="inlineStr"/>
+      <c r="K27" s="30" t="inlineStr"/>
       <c r="L27" s="20" t="n">
         <v>79.0</v>
       </c>
@@ -2264,11 +2255,11 @@
       <c r="Z27" s="20" t="inlineStr"/>
       <c r="AA27" s="20" t="inlineStr"/>
       <c r="AB27" s="20" t="inlineStr"/>
-      <c r="AC27" s="22" t="n">
+      <c r="AC27" s="21" t="n">
         <v>81.0</v>
       </c>
-      <c r="AD27" s="22" t="inlineStr"/>
-      <c r="AE27" s="22" t="inlineStr"/>
+      <c r="AD27" s="21" t="inlineStr"/>
+      <c r="AE27" s="21" t="inlineStr"/>
     </row>
     <row r="28" customHeight="1" ht="15">
       <c r="A28" s="19" t="inlineStr">
@@ -2313,11 +2304,11 @@
       <c r="Z28" s="20" t="inlineStr"/>
       <c r="AA28" s="20" t="inlineStr"/>
       <c r="AB28" s="20" t="inlineStr"/>
-      <c r="AC28" s="22" t="n">
+      <c r="AC28" s="21" t="n">
         <v>28.0</v>
       </c>
-      <c r="AD28" s="22" t="inlineStr"/>
-      <c r="AE28" s="22" t="inlineStr"/>
+      <c r="AD28" s="21" t="inlineStr"/>
+      <c r="AE28" s="21" t="inlineStr"/>
     </row>
     <row r="29" customHeight="1" ht="15">
       <c r="A29" s="19" t="inlineStr">
@@ -2334,39 +2325,39 @@
       <c r="F29" s="20" t="n"/>
       <c r="G29" s="20" t="inlineStr"/>
       <c r="H29" s="20" t="inlineStr"/>
-      <c r="I29" s="26" t="n">
+      <c r="I29" s="25" t="n">
         <v>157.6</v>
       </c>
-      <c r="J29" s="26" t="inlineStr"/>
-      <c r="K29" s="26" t="inlineStr"/>
-      <c r="L29" s="26" t="n">
+      <c r="J29" s="25" t="inlineStr"/>
+      <c r="K29" s="25" t="inlineStr"/>
+      <c r="L29" s="25" t="n">
         <v>158.5</v>
       </c>
-      <c r="M29" s="26" t="inlineStr"/>
-      <c r="N29" s="26" t="inlineStr"/>
-      <c r="O29" s="26" t="inlineStr"/>
+      <c r="M29" s="25" t="inlineStr"/>
+      <c r="N29" s="25" t="inlineStr"/>
+      <c r="O29" s="25" t="inlineStr"/>
       <c r="P29" s="20" t="n"/>
       <c r="Q29" s="20" t="inlineStr"/>
-      <c r="R29" s="26" t="n">
+      <c r="R29" s="25" t="n">
         <v>157.9</v>
       </c>
-      <c r="S29" s="26" t="inlineStr"/>
-      <c r="T29" s="26" t="inlineStr"/>
-      <c r="U29" s="26" t="n">
+      <c r="S29" s="25" t="inlineStr"/>
+      <c r="T29" s="25" t="inlineStr"/>
+      <c r="U29" s="25" t="n">
         <v>159.0</v>
       </c>
-      <c r="V29" s="26" t="inlineStr"/>
-      <c r="W29" s="26" t="inlineStr"/>
+      <c r="V29" s="25" t="inlineStr"/>
+      <c r="W29" s="25" t="inlineStr"/>
       <c r="X29" s="20" t="n"/>
       <c r="Y29" s="20" t="inlineStr"/>
       <c r="Z29" s="20" t="inlineStr"/>
       <c r="AA29" s="20" t="inlineStr"/>
       <c r="AB29" s="20" t="inlineStr"/>
-      <c r="AC29" s="27" t="n">
+      <c r="AC29" s="26" t="n">
         <v>157.8</v>
       </c>
-      <c r="AD29" s="27" t="inlineStr"/>
-      <c r="AE29" s="27" t="inlineStr"/>
+      <c r="AD29" s="26" t="inlineStr"/>
+      <c r="AE29" s="26" t="inlineStr"/>
     </row>
     <row r="30" customHeight="1" ht="15">
       <c r="A30" s="19" t="inlineStr">
@@ -2380,48 +2371,48 @@
       <c r="C30" s="19" t="inlineStr"/>
       <c r="D30" s="19" t="inlineStr"/>
       <c r="E30" s="19" t="inlineStr"/>
-      <c r="F30" s="26" t="n">
+      <c r="F30" s="25" t="n">
         <v>88.0</v>
       </c>
-      <c r="G30" s="26" t="inlineStr"/>
-      <c r="H30" s="26" t="inlineStr"/>
-      <c r="I30" s="26" t="n">
+      <c r="G30" s="25" t="inlineStr"/>
+      <c r="H30" s="25" t="inlineStr"/>
+      <c r="I30" s="25" t="n">
         <v>91.1</v>
       </c>
-      <c r="J30" s="26" t="inlineStr"/>
-      <c r="K30" s="26" t="inlineStr"/>
-      <c r="L30" s="26" t="n">
+      <c r="J30" s="25" t="inlineStr"/>
+      <c r="K30" s="25" t="inlineStr"/>
+      <c r="L30" s="25" t="n">
         <v>88.8</v>
       </c>
-      <c r="M30" s="26" t="inlineStr"/>
-      <c r="N30" s="26" t="inlineStr"/>
-      <c r="O30" s="26" t="inlineStr"/>
-      <c r="P30" s="26" t="n">
+      <c r="M30" s="25" t="inlineStr"/>
+      <c r="N30" s="25" t="inlineStr"/>
+      <c r="O30" s="25" t="inlineStr"/>
+      <c r="P30" s="25" t="n">
         <v>0.7640449438202239</v>
       </c>
-      <c r="Q30" s="26" t="inlineStr"/>
-      <c r="R30" s="26" t="n">
+      <c r="Q30" s="25" t="inlineStr"/>
+      <c r="R30" s="25" t="n">
         <v>87.5</v>
       </c>
-      <c r="S30" s="26" t="inlineStr"/>
-      <c r="T30" s="26" t="inlineStr"/>
-      <c r="U30" s="26" t="n">
+      <c r="S30" s="25" t="inlineStr"/>
+      <c r="T30" s="25" t="inlineStr"/>
+      <c r="U30" s="25" t="n">
         <v>88.5</v>
       </c>
-      <c r="V30" s="26" t="inlineStr"/>
-      <c r="W30" s="26" t="inlineStr"/>
-      <c r="X30" s="26" t="n">
+      <c r="V30" s="25" t="inlineStr"/>
+      <c r="W30" s="25" t="inlineStr"/>
+      <c r="X30" s="25" t="n">
         <v>0.5438233264320189</v>
       </c>
-      <c r="Y30" s="26" t="inlineStr"/>
-      <c r="Z30" s="26" t="inlineStr"/>
-      <c r="AA30" s="26" t="inlineStr"/>
-      <c r="AB30" s="26" t="inlineStr"/>
-      <c r="AC30" s="27" t="n">
+      <c r="Y30" s="25" t="inlineStr"/>
+      <c r="Z30" s="25" t="inlineStr"/>
+      <c r="AA30" s="25" t="inlineStr"/>
+      <c r="AB30" s="25" t="inlineStr"/>
+      <c r="AC30" s="26" t="n">
         <v>89.0</v>
       </c>
-      <c r="AD30" s="27" t="inlineStr"/>
-      <c r="AE30" s="27" t="inlineStr"/>
+      <c r="AD30" s="26" t="inlineStr"/>
+      <c r="AE30" s="26" t="inlineStr"/>
     </row>
     <row r="31" customHeight="1" ht="15">
       <c r="A31" s="19" t="inlineStr">
@@ -2435,48 +2426,48 @@
       <c r="C31" s="19" t="inlineStr"/>
       <c r="D31" s="19" t="inlineStr"/>
       <c r="E31" s="19" t="inlineStr"/>
-      <c r="F31" s="26" t="n">
+      <c r="F31" s="25" t="n">
         <v>20.0</v>
       </c>
-      <c r="G31" s="26" t="inlineStr"/>
-      <c r="H31" s="26" t="inlineStr"/>
-      <c r="I31" s="28" t="n">
+      <c r="G31" s="25" t="inlineStr"/>
+      <c r="H31" s="25" t="inlineStr"/>
+      <c r="I31" s="27" t="n">
         <v>21.1</v>
       </c>
-      <c r="J31" s="28" t="inlineStr"/>
-      <c r="K31" s="28" t="inlineStr"/>
-      <c r="L31" s="26" t="n">
+      <c r="J31" s="27" t="inlineStr"/>
+      <c r="K31" s="27" t="inlineStr"/>
+      <c r="L31" s="25" t="n">
         <v>20.7</v>
       </c>
-      <c r="M31" s="26" t="inlineStr"/>
-      <c r="N31" s="26" t="inlineStr"/>
-      <c r="O31" s="26" t="inlineStr"/>
-      <c r="P31" s="26" t="n">
+      <c r="M31" s="25" t="inlineStr"/>
+      <c r="N31" s="25" t="inlineStr"/>
+      <c r="O31" s="25" t="inlineStr"/>
+      <c r="P31" s="25" t="n">
         <v>0.6803797468354418</v>
       </c>
-      <c r="Q31" s="26" t="inlineStr"/>
-      <c r="R31" s="26" t="n">
+      <c r="Q31" s="25" t="inlineStr"/>
+      <c r="R31" s="25" t="n">
         <v>20.4</v>
       </c>
-      <c r="S31" s="26" t="inlineStr"/>
-      <c r="T31" s="26" t="inlineStr"/>
-      <c r="U31" s="26" t="n">
+      <c r="S31" s="25" t="inlineStr"/>
+      <c r="T31" s="25" t="inlineStr"/>
+      <c r="U31" s="25" t="n">
         <v>20.2</v>
       </c>
-      <c r="V31" s="26" t="inlineStr"/>
-      <c r="W31" s="26" t="inlineStr"/>
-      <c r="X31" s="26" t="n">
+      <c r="V31" s="25" t="inlineStr"/>
+      <c r="W31" s="25" t="inlineStr"/>
+      <c r="X31" s="25" t="n">
         <v>0.23772408417771018</v>
       </c>
-      <c r="Y31" s="26" t="inlineStr"/>
-      <c r="Z31" s="26" t="inlineStr"/>
-      <c r="AA31" s="26" t="inlineStr"/>
-      <c r="AB31" s="26" t="inlineStr"/>
-      <c r="AC31" s="27" t="n">
+      <c r="Y31" s="25" t="inlineStr"/>
+      <c r="Z31" s="25" t="inlineStr"/>
+      <c r="AA31" s="25" t="inlineStr"/>
+      <c r="AB31" s="25" t="inlineStr"/>
+      <c r="AC31" s="26" t="n">
         <v>20.2</v>
       </c>
-      <c r="AD31" s="27" t="inlineStr"/>
-      <c r="AE31" s="27" t="inlineStr"/>
+      <c r="AD31" s="26" t="inlineStr"/>
+      <c r="AE31" s="26" t="inlineStr"/>
     </row>
     <row r="32" customHeight="1" ht="15">
       <c r="A32" s="19" t="inlineStr">
@@ -2490,48 +2481,48 @@
       <c r="C32" s="19" t="inlineStr"/>
       <c r="D32" s="19" t="inlineStr"/>
       <c r="E32" s="19" t="inlineStr"/>
-      <c r="F32" s="26" t="n">
+      <c r="F32" s="25" t="n">
         <v>18.0</v>
       </c>
-      <c r="G32" s="26" t="inlineStr"/>
-      <c r="H32" s="26" t="inlineStr"/>
-      <c r="I32" s="26" t="n">
+      <c r="G32" s="25" t="inlineStr"/>
+      <c r="H32" s="25" t="inlineStr"/>
+      <c r="I32" s="25" t="n">
         <v>19.1</v>
       </c>
-      <c r="J32" s="26" t="inlineStr"/>
-      <c r="K32" s="26" t="inlineStr"/>
-      <c r="L32" s="26" t="n">
+      <c r="J32" s="25" t="inlineStr"/>
+      <c r="K32" s="25" t="inlineStr"/>
+      <c r="L32" s="25" t="n">
         <v>18.2</v>
       </c>
-      <c r="M32" s="26" t="inlineStr"/>
-      <c r="N32" s="26" t="inlineStr"/>
-      <c r="O32" s="26" t="inlineStr"/>
-      <c r="P32" s="26" t="n">
+      <c r="M32" s="25" t="inlineStr"/>
+      <c r="N32" s="25" t="inlineStr"/>
+      <c r="O32" s="25" t="inlineStr"/>
+      <c r="P32" s="25" t="n">
         <v>0.18421052631579116</v>
       </c>
-      <c r="Q32" s="26" t="inlineStr"/>
-      <c r="R32" s="26" t="n">
+      <c r="Q32" s="25" t="inlineStr"/>
+      <c r="R32" s="25" t="n">
         <v>17.7</v>
       </c>
-      <c r="S32" s="26" t="inlineStr"/>
-      <c r="T32" s="26" t="inlineStr"/>
-      <c r="U32" s="26" t="n">
+      <c r="S32" s="25" t="inlineStr"/>
+      <c r="T32" s="25" t="inlineStr"/>
+      <c r="U32" s="25" t="n">
         <v>17.8</v>
       </c>
-      <c r="V32" s="26" t="inlineStr"/>
-      <c r="W32" s="26" t="inlineStr"/>
-      <c r="X32" s="26" t="n">
+      <c r="V32" s="25" t="inlineStr"/>
+      <c r="W32" s="25" t="inlineStr"/>
+      <c r="X32" s="25" t="n">
         <v>-0.23232323232323182</v>
       </c>
-      <c r="Y32" s="26" t="inlineStr"/>
-      <c r="Z32" s="26" t="inlineStr"/>
-      <c r="AA32" s="26" t="inlineStr"/>
-      <c r="AB32" s="26" t="inlineStr"/>
-      <c r="AC32" s="27" t="n">
+      <c r="Y32" s="25" t="inlineStr"/>
+      <c r="Z32" s="25" t="inlineStr"/>
+      <c r="AA32" s="25" t="inlineStr"/>
+      <c r="AB32" s="25" t="inlineStr"/>
+      <c r="AC32" s="26" t="n">
         <v>18.1</v>
       </c>
-      <c r="AD32" s="27" t="inlineStr"/>
-      <c r="AE32" s="27" t="inlineStr"/>
+      <c r="AD32" s="26" t="inlineStr"/>
+      <c r="AE32" s="26" t="inlineStr"/>
     </row>
     <row r="33" customHeight="1" ht="15">
       <c r="A33" s="19" t="inlineStr">
@@ -2545,48 +2536,48 @@
       <c r="C33" s="19" t="inlineStr"/>
       <c r="D33" s="19" t="inlineStr"/>
       <c r="E33" s="19" t="inlineStr"/>
-      <c r="F33" s="26" t="n">
+      <c r="F33" s="25" t="n">
         <v>1.6</v>
       </c>
-      <c r="G33" s="26" t="inlineStr"/>
-      <c r="H33" s="26" t="inlineStr"/>
-      <c r="I33" s="28" t="n">
+      <c r="G33" s="25" t="inlineStr"/>
+      <c r="H33" s="25" t="inlineStr"/>
+      <c r="I33" s="27" t="n">
         <v>1.2</v>
       </c>
-      <c r="J33" s="28" t="inlineStr"/>
-      <c r="K33" s="28" t="inlineStr"/>
-      <c r="L33" s="26" t="n">
+      <c r="J33" s="27" t="inlineStr"/>
+      <c r="K33" s="27" t="inlineStr"/>
+      <c r="L33" s="25" t="n">
         <v>1.3</v>
       </c>
-      <c r="M33" s="26" t="inlineStr"/>
-      <c r="N33" s="26" t="inlineStr"/>
-      <c r="O33" s="26" t="inlineStr"/>
-      <c r="P33" s="26" t="n">
+      <c r="M33" s="25" t="inlineStr"/>
+      <c r="N33" s="25" t="inlineStr"/>
+      <c r="O33" s="25" t="inlineStr"/>
+      <c r="P33" s="25" t="n">
         <v>-0.34683544303797476</v>
       </c>
-      <c r="Q33" s="26" t="inlineStr"/>
-      <c r="R33" s="26" t="n">
+      <c r="Q33" s="25" t="inlineStr"/>
+      <c r="R33" s="25" t="n">
         <v>1.3</v>
       </c>
-      <c r="S33" s="26" t="inlineStr"/>
-      <c r="T33" s="26" t="inlineStr"/>
-      <c r="U33" s="26" t="n">
+      <c r="S33" s="25" t="inlineStr"/>
+      <c r="T33" s="25" t="inlineStr"/>
+      <c r="U33" s="25" t="n">
         <v>1.3</v>
       </c>
-      <c r="V33" s="26" t="inlineStr"/>
-      <c r="W33" s="26" t="inlineStr"/>
-      <c r="X33" s="26" t="n">
+      <c r="V33" s="25" t="inlineStr"/>
+      <c r="W33" s="25" t="inlineStr"/>
+      <c r="X33" s="25" t="n">
         <v>-0.25783320342946237</v>
       </c>
-      <c r="Y33" s="26" t="inlineStr"/>
-      <c r="Z33" s="26" t="inlineStr"/>
-      <c r="AA33" s="26" t="inlineStr"/>
-      <c r="AB33" s="26" t="inlineStr"/>
-      <c r="AC33" s="27" t="n">
+      <c r="Y33" s="25" t="inlineStr"/>
+      <c r="Z33" s="25" t="inlineStr"/>
+      <c r="AA33" s="25" t="inlineStr"/>
+      <c r="AB33" s="25" t="inlineStr"/>
+      <c r="AC33" s="26" t="n">
         <v>1.4</v>
       </c>
-      <c r="AD33" s="27" t="inlineStr"/>
-      <c r="AE33" s="27" t="inlineStr"/>
+      <c r="AD33" s="26" t="inlineStr"/>
+      <c r="AE33" s="26" t="inlineStr"/>
     </row>
     <row r="34" customHeight="1" ht="15">
       <c r="A34" s="19" t="inlineStr">
@@ -2605,17 +2596,17 @@
       </c>
       <c r="G34" s="20" t="inlineStr"/>
       <c r="H34" s="20" t="inlineStr"/>
-      <c r="I34" s="31" t="n">
+      <c r="I34" s="30" t="n">
         <v>121.0</v>
       </c>
-      <c r="J34" s="31" t="inlineStr"/>
-      <c r="K34" s="31" t="inlineStr"/>
-      <c r="L34" s="31" t="n">
+      <c r="J34" s="30" t="inlineStr"/>
+      <c r="K34" s="30" t="inlineStr"/>
+      <c r="L34" s="30" t="n">
         <v>160.0</v>
       </c>
-      <c r="M34" s="31" t="inlineStr"/>
-      <c r="N34" s="31" t="inlineStr"/>
-      <c r="O34" s="31" t="inlineStr"/>
+      <c r="M34" s="30" t="inlineStr"/>
+      <c r="N34" s="30" t="inlineStr"/>
+      <c r="O34" s="30" t="inlineStr"/>
       <c r="P34" s="20" t="n">
         <v>-140.0</v>
       </c>
@@ -2637,11 +2628,11 @@
       <c r="Z34" s="20" t="inlineStr"/>
       <c r="AA34" s="20" t="inlineStr"/>
       <c r="AB34" s="20" t="inlineStr"/>
-      <c r="AC34" s="22" t="n">
+      <c r="AC34" s="21" t="n">
         <v>182.0</v>
       </c>
-      <c r="AD34" s="22" t="inlineStr"/>
-      <c r="AE34" s="22" t="inlineStr"/>
+      <c r="AD34" s="21" t="inlineStr"/>
+      <c r="AE34" s="21" t="inlineStr"/>
     </row>
     <row r="35" customHeight="1" ht="15">
       <c r="A35" s="19" t="inlineStr">
@@ -2655,48 +2646,48 @@
       <c r="C35" s="19" t="inlineStr"/>
       <c r="D35" s="19" t="inlineStr"/>
       <c r="E35" s="19" t="inlineStr"/>
-      <c r="F35" s="23" t="n">
+      <c r="F35" s="22" t="n">
         <v>12.0</v>
       </c>
-      <c r="G35" s="23" t="inlineStr"/>
-      <c r="H35" s="23" t="inlineStr"/>
-      <c r="I35" s="24" t="n">
+      <c r="G35" s="22" t="inlineStr"/>
+      <c r="H35" s="22" t="inlineStr"/>
+      <c r="I35" s="23" t="n">
         <v>6.83</v>
       </c>
-      <c r="J35" s="24" t="inlineStr"/>
-      <c r="K35" s="24" t="inlineStr"/>
-      <c r="L35" s="24" t="n">
+      <c r="J35" s="23" t="inlineStr"/>
+      <c r="K35" s="23" t="inlineStr"/>
+      <c r="L35" s="23" t="n">
         <v>9.79</v>
       </c>
-      <c r="M35" s="24" t="inlineStr"/>
-      <c r="N35" s="24" t="inlineStr"/>
-      <c r="O35" s="24" t="inlineStr"/>
-      <c r="P35" s="23" t="n">
+      <c r="M35" s="23" t="inlineStr"/>
+      <c r="N35" s="23" t="inlineStr"/>
+      <c r="O35" s="23" t="inlineStr"/>
+      <c r="P35" s="22" t="n">
         <v>-2.2065799540933444</v>
       </c>
-      <c r="Q35" s="23" t="inlineStr"/>
-      <c r="R35" s="23" t="n">
+      <c r="Q35" s="22" t="inlineStr"/>
+      <c r="R35" s="22" t="n">
         <v>11.26</v>
       </c>
-      <c r="S35" s="23" t="inlineStr"/>
-      <c r="T35" s="23" t="inlineStr"/>
-      <c r="U35" s="23" t="n">
+      <c r="S35" s="22" t="inlineStr"/>
+      <c r="T35" s="22" t="inlineStr"/>
+      <c r="U35" s="22" t="n">
         <v>11.37</v>
       </c>
-      <c r="V35" s="23" t="inlineStr"/>
-      <c r="W35" s="23" t="inlineStr"/>
-      <c r="X35" s="23" t="n">
+      <c r="V35" s="22" t="inlineStr"/>
+      <c r="W35" s="22" t="inlineStr"/>
+      <c r="X35" s="22" t="n">
         <v>-0.6269978817639128</v>
       </c>
-      <c r="Y35" s="23" t="inlineStr"/>
-      <c r="Z35" s="23" t="inlineStr"/>
-      <c r="AA35" s="23" t="inlineStr"/>
-      <c r="AB35" s="23" t="inlineStr"/>
-      <c r="AC35" s="32" t="n">
+      <c r="Y35" s="22" t="inlineStr"/>
+      <c r="Z35" s="22" t="inlineStr"/>
+      <c r="AA35" s="22" t="inlineStr"/>
+      <c r="AB35" s="22" t="inlineStr"/>
+      <c r="AC35" s="31" t="n">
         <v>11.13</v>
       </c>
-      <c r="AD35" s="32" t="inlineStr"/>
-      <c r="AE35" s="32" t="inlineStr"/>
+      <c r="AD35" s="31" t="inlineStr"/>
+      <c r="AE35" s="31" t="inlineStr"/>
     </row>
     <row r="36" customHeight="1" ht="15">
       <c r="A36" s="19" t="inlineStr">
@@ -2747,11 +2738,11 @@
       <c r="Z36" s="20" t="inlineStr"/>
       <c r="AA36" s="20" t="inlineStr"/>
       <c r="AB36" s="20" t="inlineStr"/>
-      <c r="AC36" s="22" t="n">
+      <c r="AC36" s="21" t="n">
         <v>118.0</v>
       </c>
-      <c r="AD36" s="22" t="inlineStr"/>
-      <c r="AE36" s="22" t="inlineStr"/>
+      <c r="AD36" s="21" t="inlineStr"/>
+      <c r="AE36" s="21" t="inlineStr"/>
     </row>
     <row r="37" customHeight="1" ht="15">
       <c r="A37" s="19" t="inlineStr">
@@ -2802,11 +2793,11 @@
       <c r="Z37" s="20" t="inlineStr"/>
       <c r="AA37" s="20" t="inlineStr"/>
       <c r="AB37" s="20" t="inlineStr"/>
-      <c r="AC37" s="22" t="n">
+      <c r="AC37" s="21" t="n">
         <v>1437.0</v>
       </c>
-      <c r="AD37" s="22" t="inlineStr"/>
-      <c r="AE37" s="22" t="inlineStr"/>
+      <c r="AD37" s="21" t="inlineStr"/>
+      <c r="AE37" s="21" t="inlineStr"/>
     </row>
     <row r="38" customHeight="1" ht="15">
       <c r="A38" s="19" t="inlineStr">
@@ -2820,48 +2811,48 @@
       <c r="C38" s="19" t="inlineStr"/>
       <c r="D38" s="19" t="inlineStr"/>
       <c r="E38" s="19" t="inlineStr"/>
-      <c r="F38" s="26" t="n">
+      <c r="F38" s="25" t="n">
         <v>11.8</v>
       </c>
-      <c r="G38" s="26" t="inlineStr"/>
-      <c r="H38" s="26" t="inlineStr"/>
-      <c r="I38" s="26" t="n">
+      <c r="G38" s="25" t="inlineStr"/>
+      <c r="H38" s="25" t="inlineStr"/>
+      <c r="I38" s="25" t="n">
         <v>12.4</v>
       </c>
-      <c r="J38" s="26" t="inlineStr"/>
-      <c r="K38" s="26" t="inlineStr"/>
-      <c r="L38" s="26" t="n">
+      <c r="J38" s="25" t="inlineStr"/>
+      <c r="K38" s="25" t="inlineStr"/>
+      <c r="L38" s="25" t="n">
         <v>12.1</v>
       </c>
-      <c r="M38" s="26" t="inlineStr"/>
-      <c r="N38" s="26" t="inlineStr"/>
-      <c r="O38" s="26" t="inlineStr"/>
-      <c r="P38" s="26" t="n">
+      <c r="M38" s="25" t="inlineStr"/>
+      <c r="N38" s="25" t="inlineStr"/>
+      <c r="O38" s="25" t="inlineStr"/>
+      <c r="P38" s="25" t="n">
         <v>0.2583153347732168</v>
       </c>
-      <c r="Q38" s="26" t="inlineStr"/>
-      <c r="R38" s="26" t="n">
+      <c r="Q38" s="25" t="inlineStr"/>
+      <c r="R38" s="25" t="n">
         <v>12.0</v>
       </c>
-      <c r="S38" s="26" t="inlineStr"/>
-      <c r="T38" s="26" t="inlineStr"/>
-      <c r="U38" s="26" t="n">
+      <c r="S38" s="25" t="inlineStr"/>
+      <c r="T38" s="25" t="inlineStr"/>
+      <c r="U38" s="25" t="n">
         <v>12.1</v>
       </c>
-      <c r="V38" s="26" t="inlineStr"/>
-      <c r="W38" s="26" t="inlineStr"/>
-      <c r="X38" s="26" t="n">
+      <c r="V38" s="25" t="inlineStr"/>
+      <c r="W38" s="25" t="inlineStr"/>
+      <c r="X38" s="25" t="n">
         <v>0.2950854700854695</v>
       </c>
-      <c r="Y38" s="26" t="inlineStr"/>
-      <c r="Z38" s="26" t="inlineStr"/>
-      <c r="AA38" s="26" t="inlineStr"/>
-      <c r="AB38" s="26" t="inlineStr"/>
-      <c r="AC38" s="27" t="n">
+      <c r="Y38" s="25" t="inlineStr"/>
+      <c r="Z38" s="25" t="inlineStr"/>
+      <c r="AA38" s="25" t="inlineStr"/>
+      <c r="AB38" s="25" t="inlineStr"/>
+      <c r="AC38" s="26" t="n">
         <v>12.2</v>
       </c>
-      <c r="AD38" s="27" t="inlineStr"/>
-      <c r="AE38" s="27" t="inlineStr"/>
+      <c r="AD38" s="26" t="inlineStr"/>
+      <c r="AE38" s="26" t="inlineStr"/>
     </row>
     <row r="39" customHeight="1" ht="15">
       <c r="A39" s="19" t="inlineStr">
@@ -2875,48 +2866,48 @@
       <c r="C39" s="19" t="inlineStr"/>
       <c r="D39" s="19" t="inlineStr"/>
       <c r="E39" s="19" t="inlineStr"/>
-      <c r="F39" s="26" t="n">
+      <c r="F39" s="25" t="n">
         <v>18.0</v>
       </c>
-      <c r="G39" s="26" t="inlineStr"/>
-      <c r="H39" s="26" t="inlineStr"/>
-      <c r="I39" s="26" t="n">
+      <c r="G39" s="25" t="inlineStr"/>
+      <c r="H39" s="25" t="inlineStr"/>
+      <c r="I39" s="25" t="n">
         <v>19.2</v>
       </c>
-      <c r="J39" s="26" t="inlineStr"/>
-      <c r="K39" s="26" t="inlineStr"/>
-      <c r="L39" s="26" t="n">
+      <c r="J39" s="25" t="inlineStr"/>
+      <c r="K39" s="25" t="inlineStr"/>
+      <c r="L39" s="25" t="n">
         <v>18.4</v>
       </c>
-      <c r="M39" s="26" t="inlineStr"/>
-      <c r="N39" s="26" t="inlineStr"/>
-      <c r="O39" s="26" t="inlineStr"/>
-      <c r="P39" s="26" t="n">
+      <c r="M39" s="25" t="inlineStr"/>
+      <c r="N39" s="25" t="inlineStr"/>
+      <c r="O39" s="25" t="inlineStr"/>
+      <c r="P39" s="25" t="n">
         <v>0.3651315789473699</v>
       </c>
-      <c r="Q39" s="26" t="inlineStr"/>
-      <c r="R39" s="26" t="n">
+      <c r="Q39" s="25" t="inlineStr"/>
+      <c r="R39" s="25" t="n">
         <v>18.0</v>
       </c>
-      <c r="S39" s="26" t="inlineStr"/>
-      <c r="T39" s="26" t="inlineStr"/>
-      <c r="U39" s="26" t="n">
+      <c r="S39" s="25" t="inlineStr"/>
+      <c r="T39" s="25" t="inlineStr"/>
+      <c r="U39" s="25" t="n">
         <v>17.9</v>
       </c>
-      <c r="V39" s="26" t="inlineStr"/>
-      <c r="W39" s="26" t="inlineStr"/>
-      <c r="X39" s="26" t="n">
+      <c r="V39" s="25" t="inlineStr"/>
+      <c r="W39" s="25" t="inlineStr"/>
+      <c r="X39" s="25" t="n">
         <v>-0.07284243863816187</v>
       </c>
-      <c r="Y39" s="26" t="inlineStr"/>
-      <c r="Z39" s="26" t="inlineStr"/>
-      <c r="AA39" s="26" t="inlineStr"/>
-      <c r="AB39" s="26" t="inlineStr"/>
-      <c r="AC39" s="27" t="n">
+      <c r="Y39" s="25" t="inlineStr"/>
+      <c r="Z39" s="25" t="inlineStr"/>
+      <c r="AA39" s="25" t="inlineStr"/>
+      <c r="AB39" s="25" t="inlineStr"/>
+      <c r="AC39" s="26" t="n">
         <v>18.0</v>
       </c>
-      <c r="AD39" s="27" t="inlineStr"/>
-      <c r="AE39" s="27" t="inlineStr"/>
+      <c r="AD39" s="26" t="inlineStr"/>
+      <c r="AE39" s="26" t="inlineStr"/>
     </row>
     <row r="40" customHeight="1" ht="15">
       <c r="A40" s="19" t="inlineStr">
@@ -2930,48 +2921,48 @@
       <c r="C40" s="19" t="inlineStr"/>
       <c r="D40" s="19" t="inlineStr"/>
       <c r="E40" s="19" t="inlineStr"/>
-      <c r="F40" s="26" t="n">
+      <c r="F40" s="25" t="n">
         <v>10.0</v>
       </c>
-      <c r="G40" s="26" t="inlineStr"/>
-      <c r="H40" s="26" t="inlineStr"/>
-      <c r="I40" s="28" t="n">
+      <c r="G40" s="25" t="inlineStr"/>
+      <c r="H40" s="25" t="inlineStr"/>
+      <c r="I40" s="27" t="n">
         <v>-4.5</v>
       </c>
-      <c r="J40" s="28" t="inlineStr"/>
-      <c r="K40" s="28" t="inlineStr"/>
-      <c r="L40" s="26" t="n">
+      <c r="J40" s="27" t="inlineStr"/>
+      <c r="K40" s="27" t="inlineStr"/>
+      <c r="L40" s="25" t="n">
         <v>11.5</v>
       </c>
-      <c r="M40" s="26" t="inlineStr"/>
-      <c r="N40" s="26" t="inlineStr"/>
-      <c r="O40" s="26" t="inlineStr"/>
-      <c r="P40" s="26" t="n">
+      <c r="M40" s="25" t="inlineStr"/>
+      <c r="N40" s="25" t="inlineStr"/>
+      <c r="O40" s="25" t="inlineStr"/>
+      <c r="P40" s="25" t="n">
         <v>1.535414355886548</v>
       </c>
-      <c r="Q40" s="26" t="inlineStr"/>
-      <c r="R40" s="26" t="n">
+      <c r="Q40" s="25" t="inlineStr"/>
+      <c r="R40" s="25" t="n">
         <v>11.5</v>
       </c>
-      <c r="S40" s="26" t="inlineStr"/>
-      <c r="T40" s="26" t="inlineStr"/>
-      <c r="U40" s="26" t="n">
+      <c r="S40" s="25" t="inlineStr"/>
+      <c r="T40" s="25" t="inlineStr"/>
+      <c r="U40" s="25" t="n">
         <v>11.6</v>
       </c>
-      <c r="V40" s="26" t="inlineStr"/>
-      <c r="W40" s="26" t="inlineStr"/>
-      <c r="X40" s="26" t="n">
+      <c r="V40" s="25" t="inlineStr"/>
+      <c r="W40" s="25" t="inlineStr"/>
+      <c r="X40" s="25" t="n">
         <v>1.6444236322484969</v>
       </c>
-      <c r="Y40" s="26" t="inlineStr"/>
-      <c r="Z40" s="26" t="inlineStr"/>
-      <c r="AA40" s="26" t="inlineStr"/>
-      <c r="AB40" s="26" t="inlineStr"/>
-      <c r="AC40" s="27" t="n">
+      <c r="Y40" s="25" t="inlineStr"/>
+      <c r="Z40" s="25" t="inlineStr"/>
+      <c r="AA40" s="25" t="inlineStr"/>
+      <c r="AB40" s="25" t="inlineStr"/>
+      <c r="AC40" s="26" t="n">
         <v>11.4</v>
       </c>
-      <c r="AD40" s="27" t="inlineStr"/>
-      <c r="AE40" s="27" t="inlineStr"/>
+      <c r="AD40" s="26" t="inlineStr"/>
+      <c r="AE40" s="26" t="inlineStr"/>
     </row>
     <row r="41" customHeight="1" ht="15">
       <c r="A41" s="19" t="inlineStr">
@@ -2985,42 +2976,42 @@
       <c r="C41" s="19" t="inlineStr"/>
       <c r="D41" s="19" t="inlineStr"/>
       <c r="E41" s="19" t="inlineStr"/>
-      <c r="F41" s="26" t="n"/>
-      <c r="G41" s="26" t="inlineStr"/>
-      <c r="H41" s="26" t="inlineStr"/>
-      <c r="I41" s="26" t="n">
+      <c r="F41" s="25" t="n"/>
+      <c r="G41" s="25" t="inlineStr"/>
+      <c r="H41" s="25" t="inlineStr"/>
+      <c r="I41" s="25" t="n">
         <v>22.2</v>
       </c>
-      <c r="J41" s="26" t="inlineStr"/>
-      <c r="K41" s="26" t="inlineStr"/>
-      <c r="L41" s="26" t="n">
+      <c r="J41" s="25" t="inlineStr"/>
+      <c r="K41" s="25" t="inlineStr"/>
+      <c r="L41" s="25" t="n">
         <v>9.3</v>
       </c>
-      <c r="M41" s="26" t="inlineStr"/>
-      <c r="N41" s="26" t="inlineStr"/>
-      <c r="O41" s="26" t="inlineStr"/>
-      <c r="P41" s="26" t="n"/>
-      <c r="Q41" s="26" t="inlineStr"/>
-      <c r="R41" s="26" t="n">
+      <c r="M41" s="25" t="inlineStr"/>
+      <c r="N41" s="25" t="inlineStr"/>
+      <c r="O41" s="25" t="inlineStr"/>
+      <c r="P41" s="25" t="n"/>
+      <c r="Q41" s="25" t="inlineStr"/>
+      <c r="R41" s="25" t="n">
         <v>12.3</v>
       </c>
-      <c r="S41" s="26" t="inlineStr"/>
-      <c r="T41" s="26" t="inlineStr"/>
-      <c r="U41" s="26" t="n">
+      <c r="S41" s="25" t="inlineStr"/>
+      <c r="T41" s="25" t="inlineStr"/>
+      <c r="U41" s="25" t="n">
         <v>11.3</v>
       </c>
-      <c r="V41" s="26" t="inlineStr"/>
-      <c r="W41" s="26" t="inlineStr"/>
-      <c r="X41" s="26" t="n"/>
-      <c r="Y41" s="26" t="inlineStr"/>
-      <c r="Z41" s="26" t="inlineStr"/>
-      <c r="AA41" s="26" t="inlineStr"/>
-      <c r="AB41" s="26" t="inlineStr"/>
-      <c r="AC41" s="27" t="n">
+      <c r="V41" s="25" t="inlineStr"/>
+      <c r="W41" s="25" t="inlineStr"/>
+      <c r="X41" s="25" t="n"/>
+      <c r="Y41" s="25" t="inlineStr"/>
+      <c r="Z41" s="25" t="inlineStr"/>
+      <c r="AA41" s="25" t="inlineStr"/>
+      <c r="AB41" s="25" t="inlineStr"/>
+      <c r="AC41" s="26" t="n">
         <v>11.1</v>
       </c>
-      <c r="AD41" s="27" t="inlineStr"/>
-      <c r="AE41" s="27" t="inlineStr"/>
+      <c r="AD41" s="26" t="inlineStr"/>
+      <c r="AE41" s="26" t="inlineStr"/>
     </row>
     <row r="42" customHeight="1" ht="15">
       <c r="A42" s="19" t="inlineStr">
@@ -3034,42 +3025,42 @@
       <c r="C42" s="19" t="inlineStr"/>
       <c r="D42" s="19" t="inlineStr"/>
       <c r="E42" s="19" t="inlineStr"/>
-      <c r="F42" s="26" t="n"/>
-      <c r="G42" s="26" t="inlineStr"/>
-      <c r="H42" s="26" t="inlineStr"/>
-      <c r="I42" s="26" t="n">
+      <c r="F42" s="25" t="n"/>
+      <c r="G42" s="25" t="inlineStr"/>
+      <c r="H42" s="25" t="inlineStr"/>
+      <c r="I42" s="25" t="n">
         <v>9.0</v>
       </c>
-      <c r="J42" s="26" t="inlineStr"/>
-      <c r="K42" s="26" t="inlineStr"/>
-      <c r="L42" s="26" t="n">
+      <c r="J42" s="25" t="inlineStr"/>
+      <c r="K42" s="25" t="inlineStr"/>
+      <c r="L42" s="25" t="n">
         <v>11.2</v>
       </c>
-      <c r="M42" s="26" t="inlineStr"/>
-      <c r="N42" s="26" t="inlineStr"/>
-      <c r="O42" s="26" t="inlineStr"/>
-      <c r="P42" s="26" t="n"/>
-      <c r="Q42" s="26" t="inlineStr"/>
-      <c r="R42" s="26" t="n">
+      <c r="M42" s="25" t="inlineStr"/>
+      <c r="N42" s="25" t="inlineStr"/>
+      <c r="O42" s="25" t="inlineStr"/>
+      <c r="P42" s="25" t="n"/>
+      <c r="Q42" s="25" t="inlineStr"/>
+      <c r="R42" s="25" t="n">
         <v>11.9</v>
       </c>
-      <c r="S42" s="26" t="inlineStr"/>
-      <c r="T42" s="26" t="inlineStr"/>
-      <c r="U42" s="26" t="n">
+      <c r="S42" s="25" t="inlineStr"/>
+      <c r="T42" s="25" t="inlineStr"/>
+      <c r="U42" s="25" t="n">
         <v>11.4</v>
       </c>
-      <c r="V42" s="26" t="inlineStr"/>
-      <c r="W42" s="26" t="inlineStr"/>
-      <c r="X42" s="26" t="n"/>
-      <c r="Y42" s="26" t="inlineStr"/>
-      <c r="Z42" s="26" t="inlineStr"/>
-      <c r="AA42" s="26" t="inlineStr"/>
-      <c r="AB42" s="26" t="inlineStr"/>
-      <c r="AC42" s="27" t="n">
+      <c r="V42" s="25" t="inlineStr"/>
+      <c r="W42" s="25" t="inlineStr"/>
+      <c r="X42" s="25" t="n"/>
+      <c r="Y42" s="25" t="inlineStr"/>
+      <c r="Z42" s="25" t="inlineStr"/>
+      <c r="AA42" s="25" t="inlineStr"/>
+      <c r="AB42" s="25" t="inlineStr"/>
+      <c r="AC42" s="26" t="n">
         <v>11.1</v>
       </c>
-      <c r="AD42" s="27" t="inlineStr"/>
-      <c r="AE42" s="27" t="inlineStr"/>
+      <c r="AD42" s="26" t="inlineStr"/>
+      <c r="AE42" s="26" t="inlineStr"/>
     </row>
     <row r="43" customHeight="1" ht="15">
       <c r="A43" s="19" t="inlineStr">
@@ -3083,42 +3074,42 @@
       <c r="C43" s="19" t="inlineStr"/>
       <c r="D43" s="19" t="inlineStr"/>
       <c r="E43" s="19" t="inlineStr"/>
-      <c r="F43" s="26" t="n"/>
-      <c r="G43" s="26" t="inlineStr"/>
-      <c r="H43" s="26" t="inlineStr"/>
-      <c r="I43" s="26" t="n">
+      <c r="F43" s="25" t="n"/>
+      <c r="G43" s="25" t="inlineStr"/>
+      <c r="H43" s="25" t="inlineStr"/>
+      <c r="I43" s="25" t="n">
         <v>1.9</v>
       </c>
-      <c r="J43" s="26" t="inlineStr"/>
-      <c r="K43" s="26" t="inlineStr"/>
-      <c r="L43" s="26" t="n">
+      <c r="J43" s="25" t="inlineStr"/>
+      <c r="K43" s="25" t="inlineStr"/>
+      <c r="L43" s="25" t="n">
         <v>2.3</v>
       </c>
-      <c r="M43" s="26" t="inlineStr"/>
-      <c r="N43" s="26" t="inlineStr"/>
-      <c r="O43" s="26" t="inlineStr"/>
-      <c r="P43" s="26" t="n"/>
-      <c r="Q43" s="26" t="inlineStr"/>
-      <c r="R43" s="26" t="n">
+      <c r="M43" s="25" t="inlineStr"/>
+      <c r="N43" s="25" t="inlineStr"/>
+      <c r="O43" s="25" t="inlineStr"/>
+      <c r="P43" s="25" t="n"/>
+      <c r="Q43" s="25" t="inlineStr"/>
+      <c r="R43" s="25" t="n">
         <v>2.4</v>
       </c>
-      <c r="S43" s="26" t="inlineStr"/>
-      <c r="T43" s="26" t="inlineStr"/>
-      <c r="U43" s="26" t="n">
+      <c r="S43" s="25" t="inlineStr"/>
+      <c r="T43" s="25" t="inlineStr"/>
+      <c r="U43" s="25" t="n">
         <v>2.3</v>
       </c>
-      <c r="V43" s="26" t="inlineStr"/>
-      <c r="W43" s="26" t="inlineStr"/>
-      <c r="X43" s="26" t="n"/>
-      <c r="Y43" s="26" t="inlineStr"/>
-      <c r="Z43" s="26" t="inlineStr"/>
-      <c r="AA43" s="26" t="inlineStr"/>
-      <c r="AB43" s="26" t="inlineStr"/>
-      <c r="AC43" s="27" t="n">
+      <c r="V43" s="25" t="inlineStr"/>
+      <c r="W43" s="25" t="inlineStr"/>
+      <c r="X43" s="25" t="n"/>
+      <c r="Y43" s="25" t="inlineStr"/>
+      <c r="Z43" s="25" t="inlineStr"/>
+      <c r="AA43" s="25" t="inlineStr"/>
+      <c r="AB43" s="25" t="inlineStr"/>
+      <c r="AC43" s="26" t="n">
         <v>2.3</v>
       </c>
-      <c r="AD43" s="27" t="inlineStr"/>
-      <c r="AE43" s="27" t="inlineStr"/>
+      <c r="AD43" s="26" t="inlineStr"/>
+      <c r="AE43" s="26" t="inlineStr"/>
     </row>
     <row r="44" customHeight="1" ht="15">
       <c r="A44" s="19" t="inlineStr">
@@ -3132,42 +3123,42 @@
       <c r="C44" s="19" t="inlineStr"/>
       <c r="D44" s="19" t="inlineStr"/>
       <c r="E44" s="19" t="inlineStr"/>
-      <c r="F44" s="26" t="n"/>
-      <c r="G44" s="26" t="inlineStr"/>
-      <c r="H44" s="26" t="inlineStr"/>
-      <c r="I44" s="26" t="n">
+      <c r="F44" s="25" t="n"/>
+      <c r="G44" s="25" t="inlineStr"/>
+      <c r="H44" s="25" t="inlineStr"/>
+      <c r="I44" s="25" t="n">
         <v>3.1</v>
       </c>
-      <c r="J44" s="26" t="inlineStr"/>
-      <c r="K44" s="26" t="inlineStr"/>
-      <c r="L44" s="26" t="n">
+      <c r="J44" s="25" t="inlineStr"/>
+      <c r="K44" s="25" t="inlineStr"/>
+      <c r="L44" s="25" t="n">
         <v>3.6</v>
       </c>
-      <c r="M44" s="26" t="inlineStr"/>
-      <c r="N44" s="26" t="inlineStr"/>
-      <c r="O44" s="26" t="inlineStr"/>
-      <c r="P44" s="26" t="n"/>
-      <c r="Q44" s="26" t="inlineStr"/>
-      <c r="R44" s="26" t="n">
+      <c r="M44" s="25" t="inlineStr"/>
+      <c r="N44" s="25" t="inlineStr"/>
+      <c r="O44" s="25" t="inlineStr"/>
+      <c r="P44" s="25" t="n"/>
+      <c r="Q44" s="25" t="inlineStr"/>
+      <c r="R44" s="25" t="n">
         <v>3.8</v>
       </c>
-      <c r="S44" s="26" t="inlineStr"/>
-      <c r="T44" s="26" t="inlineStr"/>
-      <c r="U44" s="26" t="n">
+      <c r="S44" s="25" t="inlineStr"/>
+      <c r="T44" s="25" t="inlineStr"/>
+      <c r="U44" s="25" t="n">
         <v>3.7</v>
       </c>
-      <c r="V44" s="26" t="inlineStr"/>
-      <c r="W44" s="26" t="inlineStr"/>
-      <c r="X44" s="26" t="n"/>
-      <c r="Y44" s="26" t="inlineStr"/>
-      <c r="Z44" s="26" t="inlineStr"/>
-      <c r="AA44" s="26" t="inlineStr"/>
-      <c r="AB44" s="26" t="inlineStr"/>
-      <c r="AC44" s="27" t="n">
+      <c r="V44" s="25" t="inlineStr"/>
+      <c r="W44" s="25" t="inlineStr"/>
+      <c r="X44" s="25" t="n"/>
+      <c r="Y44" s="25" t="inlineStr"/>
+      <c r="Z44" s="25" t="inlineStr"/>
+      <c r="AA44" s="25" t="inlineStr"/>
+      <c r="AB44" s="25" t="inlineStr"/>
+      <c r="AC44" s="26" t="n">
         <v>3.6</v>
       </c>
-      <c r="AD44" s="27" t="inlineStr"/>
-      <c r="AE44" s="27" t="inlineStr"/>
+      <c r="AD44" s="26" t="inlineStr"/>
+      <c r="AE44" s="26" t="inlineStr"/>
     </row>
     <row r="45" customHeight="1" ht="15">
       <c r="A45" s="19" t="inlineStr">
@@ -3218,11 +3209,11 @@
       <c r="Z45" s="20" t="inlineStr"/>
       <c r="AA45" s="20" t="inlineStr"/>
       <c r="AB45" s="20" t="inlineStr"/>
-      <c r="AC45" s="22" t="n">
+      <c r="AC45" s="21" t="n">
         <v>30.0</v>
       </c>
-      <c r="AD45" s="22" t="inlineStr"/>
-      <c r="AE45" s="22" t="inlineStr"/>
+      <c r="AD45" s="21" t="inlineStr"/>
+      <c r="AE45" s="21" t="inlineStr"/>
     </row>
     <row r="46" customHeight="1" ht="15">
       <c r="A46" s="19" t="inlineStr">
@@ -3267,11 +3258,11 @@
       <c r="Z46" s="20" t="inlineStr"/>
       <c r="AA46" s="20" t="inlineStr"/>
       <c r="AB46" s="20" t="inlineStr"/>
-      <c r="AC46" s="22" t="n">
+      <c r="AC46" s="21" t="n">
         <v>23.0</v>
       </c>
-      <c r="AD46" s="22" t="inlineStr"/>
-      <c r="AE46" s="22" t="inlineStr"/>
+      <c r="AD46" s="21" t="inlineStr"/>
+      <c r="AE46" s="21" t="inlineStr"/>
     </row>
     <row r="47" customHeight="1" ht="15">
       <c r="A47" s="19" t="inlineStr">
@@ -3322,11 +3313,11 @@
       <c r="Z47" s="20" t="inlineStr"/>
       <c r="AA47" s="20" t="inlineStr"/>
       <c r="AB47" s="20" t="inlineStr"/>
-      <c r="AC47" s="22" t="n">
+      <c r="AC47" s="21" t="n">
         <v>118.0</v>
       </c>
-      <c r="AD47" s="22" t="inlineStr"/>
-      <c r="AE47" s="22" t="inlineStr"/>
+      <c r="AD47" s="21" t="inlineStr"/>
+      <c r="AE47" s="21" t="inlineStr"/>
     </row>
     <row r="48" customHeight="1" ht="15">
       <c r="A48" s="19" t="inlineStr">
@@ -3340,48 +3331,48 @@
       <c r="C48" s="19" t="inlineStr"/>
       <c r="D48" s="19" t="inlineStr"/>
       <c r="E48" s="19" t="inlineStr"/>
-      <c r="F48" s="26" t="n">
+      <c r="F48" s="25" t="n">
         <v>12.0</v>
       </c>
-      <c r="G48" s="26" t="inlineStr"/>
-      <c r="H48" s="26" t="inlineStr"/>
-      <c r="I48" s="26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J48" s="26" t="inlineStr"/>
-      <c r="K48" s="26" t="inlineStr"/>
-      <c r="L48" s="26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="M48" s="26" t="inlineStr"/>
-      <c r="N48" s="26" t="inlineStr"/>
-      <c r="O48" s="26" t="inlineStr"/>
-      <c r="P48" s="26" t="n">
-        <v>0.5435488787322438</v>
-      </c>
-      <c r="Q48" s="26" t="inlineStr"/>
-      <c r="R48" s="26" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="S48" s="26" t="inlineStr"/>
-      <c r="T48" s="26" t="inlineStr"/>
-      <c r="U48" s="29" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="V48" s="29" t="inlineStr"/>
-      <c r="W48" s="29" t="inlineStr"/>
-      <c r="X48" s="26" t="n">
-        <v>2.1097669268423065</v>
-      </c>
-      <c r="Y48" s="26" t="inlineStr"/>
-      <c r="Z48" s="26" t="inlineStr"/>
-      <c r="AA48" s="26" t="inlineStr"/>
-      <c r="AB48" s="26" t="inlineStr"/>
-      <c r="AC48" s="33" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="AD48" s="33" t="inlineStr"/>
-      <c r="AE48" s="33" t="inlineStr"/>
+      <c r="G48" s="25" t="inlineStr"/>
+      <c r="H48" s="25" t="inlineStr"/>
+      <c r="I48" s="25" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J48" s="25" t="inlineStr"/>
+      <c r="K48" s="25" t="inlineStr"/>
+      <c r="L48" s="25" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="M48" s="25" t="inlineStr"/>
+      <c r="N48" s="25" t="inlineStr"/>
+      <c r="O48" s="25" t="inlineStr"/>
+      <c r="P48" s="25" t="n">
+        <v>0.7310117873441673</v>
+      </c>
+      <c r="Q48" s="25" t="inlineStr"/>
+      <c r="R48" s="25" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="S48" s="25" t="inlineStr"/>
+      <c r="T48" s="25" t="inlineStr"/>
+      <c r="U48" s="28" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="V48" s="28" t="inlineStr"/>
+      <c r="W48" s="28" t="inlineStr"/>
+      <c r="X48" s="25" t="n">
+        <v>2.156724017852248</v>
+      </c>
+      <c r="Y48" s="25" t="inlineStr"/>
+      <c r="Z48" s="25" t="inlineStr"/>
+      <c r="AA48" s="25" t="inlineStr"/>
+      <c r="AB48" s="25" t="inlineStr"/>
+      <c r="AC48" s="32" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="AD48" s="32" t="inlineStr"/>
+      <c r="AE48" s="32" t="inlineStr"/>
     </row>
     <row r="49" customHeight="1" ht="15">
       <c r="A49" s="19" t="inlineStr">
@@ -3395,42 +3386,42 @@
       <c r="C49" s="19" t="inlineStr"/>
       <c r="D49" s="19" t="inlineStr"/>
       <c r="E49" s="19" t="inlineStr"/>
-      <c r="F49" s="26" t="n"/>
-      <c r="G49" s="26" t="inlineStr"/>
-      <c r="H49" s="26" t="inlineStr"/>
-      <c r="I49" s="26" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J49" s="26" t="inlineStr"/>
-      <c r="K49" s="26" t="inlineStr"/>
-      <c r="L49" s="26" t="n">
+      <c r="F49" s="25" t="n"/>
+      <c r="G49" s="25" t="inlineStr"/>
+      <c r="H49" s="25" t="inlineStr"/>
+      <c r="I49" s="25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J49" s="25" t="inlineStr"/>
+      <c r="K49" s="25" t="inlineStr"/>
+      <c r="L49" s="25" t="n">
         <v>4.7</v>
       </c>
-      <c r="M49" s="26" t="inlineStr"/>
-      <c r="N49" s="26" t="inlineStr"/>
-      <c r="O49" s="26" t="inlineStr"/>
-      <c r="P49" s="26" t="n"/>
-      <c r="Q49" s="26" t="inlineStr"/>
-      <c r="R49" s="26" t="n">
+      <c r="M49" s="25" t="inlineStr"/>
+      <c r="N49" s="25" t="inlineStr"/>
+      <c r="O49" s="25" t="inlineStr"/>
+      <c r="P49" s="25" t="n"/>
+      <c r="Q49" s="25" t="inlineStr"/>
+      <c r="R49" s="25" t="n">
         <v>4.6</v>
       </c>
-      <c r="S49" s="26" t="inlineStr"/>
-      <c r="T49" s="26" t="inlineStr"/>
-      <c r="U49" s="26" t="n">
+      <c r="S49" s="25" t="inlineStr"/>
+      <c r="T49" s="25" t="inlineStr"/>
+      <c r="U49" s="25" t="n">
         <v>4.2</v>
       </c>
-      <c r="V49" s="26" t="inlineStr"/>
-      <c r="W49" s="26" t="inlineStr"/>
-      <c r="X49" s="26" t="n"/>
-      <c r="Y49" s="26" t="inlineStr"/>
-      <c r="Z49" s="26" t="inlineStr"/>
-      <c r="AA49" s="26" t="inlineStr"/>
-      <c r="AB49" s="26" t="inlineStr"/>
-      <c r="AC49" s="27" t="n">
+      <c r="V49" s="25" t="inlineStr"/>
+      <c r="W49" s="25" t="inlineStr"/>
+      <c r="X49" s="25" t="n"/>
+      <c r="Y49" s="25" t="inlineStr"/>
+      <c r="Z49" s="25" t="inlineStr"/>
+      <c r="AA49" s="25" t="inlineStr"/>
+      <c r="AB49" s="25" t="inlineStr"/>
+      <c r="AC49" s="26" t="n">
         <v>4.0</v>
       </c>
-      <c r="AD49" s="27" t="inlineStr"/>
-      <c r="AE49" s="27" t="inlineStr"/>
+      <c r="AD49" s="26" t="inlineStr"/>
+      <c r="AE49" s="26" t="inlineStr"/>
     </row>
     <row r="50" customHeight="1" ht="15">
       <c r="A50" s="19" t="inlineStr">
@@ -3444,42 +3435,42 @@
       <c r="C50" s="19" t="inlineStr"/>
       <c r="D50" s="19" t="inlineStr"/>
       <c r="E50" s="19" t="inlineStr"/>
-      <c r="F50" s="26" t="n"/>
-      <c r="G50" s="26" t="inlineStr"/>
-      <c r="H50" s="26" t="inlineStr"/>
-      <c r="I50" s="26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J50" s="26" t="inlineStr"/>
-      <c r="K50" s="26" t="inlineStr"/>
-      <c r="L50" s="26" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="M50" s="26" t="inlineStr"/>
-      <c r="N50" s="26" t="inlineStr"/>
-      <c r="O50" s="26" t="inlineStr"/>
-      <c r="P50" s="26" t="n"/>
-      <c r="Q50" s="26" t="inlineStr"/>
-      <c r="R50" s="26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S50" s="26" t="inlineStr"/>
-      <c r="T50" s="26" t="inlineStr"/>
-      <c r="U50" s="26" t="n">
+      <c r="F50" s="25" t="n"/>
+      <c r="G50" s="25" t="inlineStr"/>
+      <c r="H50" s="25" t="inlineStr"/>
+      <c r="I50" s="25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J50" s="25" t="inlineStr"/>
+      <c r="K50" s="25" t="inlineStr"/>
+      <c r="L50" s="25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M50" s="25" t="inlineStr"/>
+      <c r="N50" s="25" t="inlineStr"/>
+      <c r="O50" s="25" t="inlineStr"/>
+      <c r="P50" s="25" t="n"/>
+      <c r="Q50" s="25" t="inlineStr"/>
+      <c r="R50" s="25" t="n">
         <v>2.5</v>
       </c>
-      <c r="V50" s="26" t="inlineStr"/>
-      <c r="W50" s="26" t="inlineStr"/>
-      <c r="X50" s="26" t="n"/>
-      <c r="Y50" s="26" t="inlineStr"/>
-      <c r="Z50" s="26" t="inlineStr"/>
-      <c r="AA50" s="26" t="inlineStr"/>
-      <c r="AB50" s="26" t="inlineStr"/>
-      <c r="AC50" s="27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD50" s="27" t="inlineStr"/>
-      <c r="AE50" s="27" t="inlineStr"/>
+      <c r="S50" s="25" t="inlineStr"/>
+      <c r="T50" s="25" t="inlineStr"/>
+      <c r="U50" s="25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V50" s="25" t="inlineStr"/>
+      <c r="W50" s="25" t="inlineStr"/>
+      <c r="X50" s="25" t="n"/>
+      <c r="Y50" s="25" t="inlineStr"/>
+      <c r="Z50" s="25" t="inlineStr"/>
+      <c r="AA50" s="25" t="inlineStr"/>
+      <c r="AB50" s="25" t="inlineStr"/>
+      <c r="AC50" s="26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD50" s="26" t="inlineStr"/>
+      <c r="AE50" s="26" t="inlineStr"/>
     </row>
     <row r="51" customHeight="1" ht="15">
       <c r="A51" s="19" t="inlineStr">
@@ -3493,42 +3484,42 @@
       <c r="C51" s="19" t="inlineStr"/>
       <c r="D51" s="19" t="inlineStr"/>
       <c r="E51" s="19" t="inlineStr"/>
-      <c r="F51" s="26" t="n"/>
-      <c r="G51" s="26" t="inlineStr"/>
-      <c r="H51" s="26" t="inlineStr"/>
-      <c r="I51" s="26" t="n">
+      <c r="F51" s="25" t="n"/>
+      <c r="G51" s="25" t="inlineStr"/>
+      <c r="H51" s="25" t="inlineStr"/>
+      <c r="I51" s="25" t="n">
         <v>0.8</v>
       </c>
-      <c r="J51" s="26" t="inlineStr"/>
-      <c r="K51" s="26" t="inlineStr"/>
-      <c r="L51" s="26" t="n">
+      <c r="J51" s="25" t="inlineStr"/>
+      <c r="K51" s="25" t="inlineStr"/>
+      <c r="L51" s="25" t="n">
         <v>3.7</v>
       </c>
-      <c r="M51" s="26" t="inlineStr"/>
-      <c r="N51" s="26" t="inlineStr"/>
-      <c r="O51" s="26" t="inlineStr"/>
-      <c r="P51" s="26" t="n"/>
-      <c r="Q51" s="26" t="inlineStr"/>
-      <c r="R51" s="26" t="n">
+      <c r="M51" s="25" t="inlineStr"/>
+      <c r="N51" s="25" t="inlineStr"/>
+      <c r="O51" s="25" t="inlineStr"/>
+      <c r="P51" s="25" t="n"/>
+      <c r="Q51" s="25" t="inlineStr"/>
+      <c r="R51" s="25" t="n">
         <v>4.3</v>
       </c>
-      <c r="S51" s="26" t="inlineStr"/>
-      <c r="T51" s="26" t="inlineStr"/>
-      <c r="U51" s="26" t="n">
+      <c r="S51" s="25" t="inlineStr"/>
+      <c r="T51" s="25" t="inlineStr"/>
+      <c r="U51" s="25" t="n">
         <v>4.6</v>
       </c>
-      <c r="V51" s="26" t="inlineStr"/>
-      <c r="W51" s="26" t="inlineStr"/>
-      <c r="X51" s="26" t="n"/>
-      <c r="Y51" s="26" t="inlineStr"/>
-      <c r="Z51" s="26" t="inlineStr"/>
-      <c r="AA51" s="26" t="inlineStr"/>
-      <c r="AB51" s="26" t="inlineStr"/>
-      <c r="AC51" s="27" t="n">
+      <c r="V51" s="25" t="inlineStr"/>
+      <c r="W51" s="25" t="inlineStr"/>
+      <c r="X51" s="25" t="n"/>
+      <c r="Y51" s="25" t="inlineStr"/>
+      <c r="Z51" s="25" t="inlineStr"/>
+      <c r="AA51" s="25" t="inlineStr"/>
+      <c r="AB51" s="25" t="inlineStr"/>
+      <c r="AC51" s="26" t="n">
         <v>5.6</v>
       </c>
-      <c r="AD51" s="27" t="inlineStr"/>
-      <c r="AE51" s="27" t="inlineStr"/>
+      <c r="AD51" s="26" t="inlineStr"/>
+      <c r="AE51" s="26" t="inlineStr"/>
     </row>
     <row r="52" customHeight="1" ht="15">
       <c r="A52" s="19" t="inlineStr">
@@ -3542,42 +3533,42 @@
       <c r="C52" s="19" t="inlineStr"/>
       <c r="D52" s="19" t="inlineStr"/>
       <c r="E52" s="19" t="inlineStr"/>
-      <c r="F52" s="26" t="n"/>
-      <c r="G52" s="26" t="inlineStr"/>
-      <c r="H52" s="26" t="inlineStr"/>
-      <c r="I52" s="26" t="n">
+      <c r="F52" s="25" t="n"/>
+      <c r="G52" s="25" t="inlineStr"/>
+      <c r="H52" s="25" t="inlineStr"/>
+      <c r="I52" s="25" t="n">
         <v>0.4</v>
       </c>
-      <c r="J52" s="26" t="inlineStr"/>
-      <c r="K52" s="26" t="inlineStr"/>
-      <c r="L52" s="26" t="n">
+      <c r="J52" s="25" t="inlineStr"/>
+      <c r="K52" s="25" t="inlineStr"/>
+      <c r="L52" s="25" t="n">
         <v>1.8</v>
       </c>
-      <c r="M52" s="26" t="inlineStr"/>
-      <c r="N52" s="26" t="inlineStr"/>
-      <c r="O52" s="26" t="inlineStr"/>
-      <c r="P52" s="26" t="n"/>
-      <c r="Q52" s="26" t="inlineStr"/>
-      <c r="R52" s="26" t="n">
+      <c r="M52" s="25" t="inlineStr"/>
+      <c r="N52" s="25" t="inlineStr"/>
+      <c r="O52" s="25" t="inlineStr"/>
+      <c r="P52" s="25" t="n"/>
+      <c r="Q52" s="25" t="inlineStr"/>
+      <c r="R52" s="25" t="n">
         <v>2.2</v>
       </c>
-      <c r="S52" s="26" t="inlineStr"/>
-      <c r="T52" s="26" t="inlineStr"/>
-      <c r="U52" s="26" t="n">
+      <c r="S52" s="25" t="inlineStr"/>
+      <c r="T52" s="25" t="inlineStr"/>
+      <c r="U52" s="25" t="n">
         <v>2.2</v>
       </c>
-      <c r="V52" s="26" t="inlineStr"/>
-      <c r="W52" s="26" t="inlineStr"/>
-      <c r="X52" s="26" t="n"/>
-      <c r="Y52" s="26" t="inlineStr"/>
-      <c r="Z52" s="26" t="inlineStr"/>
-      <c r="AA52" s="26" t="inlineStr"/>
-      <c r="AB52" s="26" t="inlineStr"/>
-      <c r="AC52" s="27" t="n">
+      <c r="V52" s="25" t="inlineStr"/>
+      <c r="W52" s="25" t="inlineStr"/>
+      <c r="X52" s="25" t="n"/>
+      <c r="Y52" s="25" t="inlineStr"/>
+      <c r="Z52" s="25" t="inlineStr"/>
+      <c r="AA52" s="25" t="inlineStr"/>
+      <c r="AB52" s="25" t="inlineStr"/>
+      <c r="AC52" s="26" t="n">
         <v>2.6</v>
       </c>
-      <c r="AD52" s="27" t="inlineStr"/>
-      <c r="AE52" s="27" t="inlineStr"/>
+      <c r="AD52" s="26" t="inlineStr"/>
+      <c r="AE52" s="26" t="inlineStr"/>
     </row>
     <row r="53" customHeight="1" ht="15">
       <c r="A53" s="19" t="inlineStr">
@@ -3591,42 +3582,42 @@
       <c r="C53" s="19" t="inlineStr"/>
       <c r="D53" s="19" t="inlineStr"/>
       <c r="E53" s="19" t="inlineStr"/>
-      <c r="F53" s="26" t="n"/>
-      <c r="G53" s="26" t="inlineStr"/>
-      <c r="H53" s="26" t="inlineStr"/>
-      <c r="I53" s="26" t="n">
+      <c r="F53" s="25" t="n"/>
+      <c r="G53" s="25" t="inlineStr"/>
+      <c r="H53" s="25" t="inlineStr"/>
+      <c r="I53" s="25" t="n">
         <v>0.4</v>
       </c>
-      <c r="J53" s="26" t="inlineStr"/>
-      <c r="K53" s="26" t="inlineStr"/>
-      <c r="L53" s="26" t="n">
+      <c r="J53" s="25" t="inlineStr"/>
+      <c r="K53" s="25" t="inlineStr"/>
+      <c r="L53" s="25" t="n">
         <v>1.9</v>
       </c>
-      <c r="M53" s="26" t="inlineStr"/>
-      <c r="N53" s="26" t="inlineStr"/>
-      <c r="O53" s="26" t="inlineStr"/>
-      <c r="P53" s="26" t="n"/>
-      <c r="Q53" s="26" t="inlineStr"/>
-      <c r="R53" s="26" t="n">
+      <c r="M53" s="25" t="inlineStr"/>
+      <c r="N53" s="25" t="inlineStr"/>
+      <c r="O53" s="25" t="inlineStr"/>
+      <c r="P53" s="25" t="n"/>
+      <c r="Q53" s="25" t="inlineStr"/>
+      <c r="R53" s="25" t="n">
         <v>2.1</v>
       </c>
-      <c r="S53" s="26" t="inlineStr"/>
-      <c r="T53" s="26" t="inlineStr"/>
-      <c r="U53" s="26" t="n">
+      <c r="S53" s="25" t="inlineStr"/>
+      <c r="T53" s="25" t="inlineStr"/>
+      <c r="U53" s="25" t="n">
         <v>2.4</v>
       </c>
-      <c r="V53" s="26" t="inlineStr"/>
-      <c r="W53" s="26" t="inlineStr"/>
-      <c r="X53" s="26" t="n"/>
-      <c r="Y53" s="26" t="inlineStr"/>
-      <c r="Z53" s="26" t="inlineStr"/>
-      <c r="AA53" s="26" t="inlineStr"/>
-      <c r="AB53" s="26" t="inlineStr"/>
-      <c r="AC53" s="27" t="n">
+      <c r="V53" s="25" t="inlineStr"/>
+      <c r="W53" s="25" t="inlineStr"/>
+      <c r="X53" s="25" t="n"/>
+      <c r="Y53" s="25" t="inlineStr"/>
+      <c r="Z53" s="25" t="inlineStr"/>
+      <c r="AA53" s="25" t="inlineStr"/>
+      <c r="AB53" s="25" t="inlineStr"/>
+      <c r="AC53" s="26" t="n">
         <v>2.9</v>
       </c>
-      <c r="AD53" s="27" t="inlineStr"/>
-      <c r="AE53" s="27" t="inlineStr"/>
+      <c r="AD53" s="26" t="inlineStr"/>
+      <c r="AE53" s="26" t="inlineStr"/>
     </row>
     <row r="54" customHeight="1" ht="15">
       <c r="A54" s="19" t="inlineStr">
@@ -3640,42 +3631,42 @@
       <c r="C54" s="19" t="inlineStr"/>
       <c r="D54" s="19" t="inlineStr"/>
       <c r="E54" s="19" t="inlineStr"/>
-      <c r="F54" s="26" t="n"/>
-      <c r="G54" s="26" t="inlineStr"/>
-      <c r="H54" s="26" t="inlineStr"/>
-      <c r="I54" s="26" t="n">
+      <c r="F54" s="25" t="n"/>
+      <c r="G54" s="25" t="inlineStr"/>
+      <c r="H54" s="25" t="inlineStr"/>
+      <c r="I54" s="25" t="n">
         <v>0.1</v>
       </c>
-      <c r="J54" s="26" t="inlineStr"/>
-      <c r="K54" s="26" t="inlineStr"/>
-      <c r="L54" s="26" t="n">
+      <c r="J54" s="25" t="inlineStr"/>
+      <c r="K54" s="25" t="inlineStr"/>
+      <c r="L54" s="25" t="n">
         <v>1.1</v>
       </c>
-      <c r="M54" s="26" t="inlineStr"/>
-      <c r="N54" s="26" t="inlineStr"/>
-      <c r="O54" s="26" t="inlineStr"/>
-      <c r="P54" s="26" t="n"/>
-      <c r="Q54" s="26" t="inlineStr"/>
-      <c r="R54" s="26" t="n">
+      <c r="M54" s="25" t="inlineStr"/>
+      <c r="N54" s="25" t="inlineStr"/>
+      <c r="O54" s="25" t="inlineStr"/>
+      <c r="P54" s="25" t="n"/>
+      <c r="Q54" s="25" t="inlineStr"/>
+      <c r="R54" s="25" t="n">
         <v>1.9</v>
       </c>
-      <c r="S54" s="26" t="inlineStr"/>
-      <c r="T54" s="26" t="inlineStr"/>
-      <c r="U54" s="26" t="n">
+      <c r="S54" s="25" t="inlineStr"/>
+      <c r="T54" s="25" t="inlineStr"/>
+      <c r="U54" s="25" t="n">
         <v>2.7</v>
       </c>
-      <c r="V54" s="26" t="inlineStr"/>
-      <c r="W54" s="26" t="inlineStr"/>
-      <c r="X54" s="26" t="n"/>
-      <c r="Y54" s="26" t="inlineStr"/>
-      <c r="Z54" s="26" t="inlineStr"/>
-      <c r="AA54" s="26" t="inlineStr"/>
-      <c r="AB54" s="26" t="inlineStr"/>
-      <c r="AC54" s="27" t="n">
+      <c r="V54" s="25" t="inlineStr"/>
+      <c r="W54" s="25" t="inlineStr"/>
+      <c r="X54" s="25" t="n"/>
+      <c r="Y54" s="25" t="inlineStr"/>
+      <c r="Z54" s="25" t="inlineStr"/>
+      <c r="AA54" s="25" t="inlineStr"/>
+      <c r="AB54" s="25" t="inlineStr"/>
+      <c r="AC54" s="26" t="n">
         <v>2.9</v>
       </c>
-      <c r="AD54" s="27" t="inlineStr"/>
-      <c r="AE54" s="27" t="inlineStr"/>
+      <c r="AD54" s="26" t="inlineStr"/>
+      <c r="AE54" s="26" t="inlineStr"/>
     </row>
     <row r="55" customHeight="1" ht="15">
       <c r="A55" s="19" t="inlineStr">
@@ -3689,48 +3680,48 @@
       <c r="C55" s="19" t="inlineStr"/>
       <c r="D55" s="19" t="inlineStr"/>
       <c r="E55" s="19" t="inlineStr"/>
-      <c r="F55" s="23" t="n">
+      <c r="F55" s="22" t="n">
         <v>2.3</v>
       </c>
-      <c r="G55" s="23" t="inlineStr"/>
-      <c r="H55" s="23" t="inlineStr"/>
-      <c r="I55" s="23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J55" s="23" t="inlineStr"/>
-      <c r="K55" s="23" t="inlineStr"/>
-      <c r="L55" s="23" t="n">
+      <c r="G55" s="22" t="inlineStr"/>
+      <c r="H55" s="22" t="inlineStr"/>
+      <c r="I55" s="22" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="J55" s="22" t="inlineStr"/>
+      <c r="K55" s="22" t="inlineStr"/>
+      <c r="L55" s="22" t="n">
         <v>2.25</v>
       </c>
-      <c r="M55" s="23" t="inlineStr"/>
-      <c r="N55" s="23" t="inlineStr"/>
-      <c r="O55" s="23" t="inlineStr"/>
-      <c r="P55" s="23" t="n">
-        <v>-0.05124733071157639</v>
-      </c>
-      <c r="Q55" s="23" t="inlineStr"/>
-      <c r="R55" s="23" t="n">
+      <c r="M55" s="22" t="inlineStr"/>
+      <c r="N55" s="22" t="inlineStr"/>
+      <c r="O55" s="22" t="inlineStr"/>
+      <c r="P55" s="22" t="n">
+        <v>-0.053841537373436665</v>
+      </c>
+      <c r="Q55" s="22" t="inlineStr"/>
+      <c r="R55" s="22" t="n">
         <v>2.25</v>
       </c>
-      <c r="S55" s="23" t="inlineStr"/>
-      <c r="T55" s="23" t="inlineStr"/>
-      <c r="U55" s="34" t="n">
+      <c r="S55" s="22" t="inlineStr"/>
+      <c r="T55" s="22" t="inlineStr"/>
+      <c r="U55" s="33" t="n">
         <v>2.24</v>
       </c>
-      <c r="V55" s="34" t="inlineStr"/>
-      <c r="W55" s="34" t="inlineStr"/>
-      <c r="X55" s="23" t="n">
-        <v>-0.05668262620289388</v>
-      </c>
-      <c r="Y55" s="23" t="inlineStr"/>
-      <c r="Z55" s="23" t="inlineStr"/>
-      <c r="AA55" s="23" t="inlineStr"/>
-      <c r="AB55" s="23" t="inlineStr"/>
-      <c r="AC55" s="35" t="n">
+      <c r="V55" s="33" t="inlineStr"/>
+      <c r="W55" s="33" t="inlineStr"/>
+      <c r="X55" s="22" t="n">
+        <v>-0.057329864847375234</v>
+      </c>
+      <c r="Y55" s="22" t="inlineStr"/>
+      <c r="Z55" s="22" t="inlineStr"/>
+      <c r="AA55" s="22" t="inlineStr"/>
+      <c r="AB55" s="22" t="inlineStr"/>
+      <c r="AC55" s="34" t="n">
         <v>2.23</v>
       </c>
-      <c r="AD55" s="35" t="inlineStr"/>
-      <c r="AE55" s="35" t="inlineStr"/>
+      <c r="AD55" s="34" t="inlineStr"/>
+      <c r="AE55" s="34" t="inlineStr"/>
     </row>
     <row r="56" customHeight="1" ht="15">
       <c r="A56" s="19" t="inlineStr">
@@ -3744,42 +3735,42 @@
       <c r="C56" s="19" t="inlineStr"/>
       <c r="D56" s="19" t="inlineStr"/>
       <c r="E56" s="19" t="inlineStr"/>
-      <c r="F56" s="23" t="n"/>
-      <c r="G56" s="23" t="inlineStr"/>
-      <c r="H56" s="23" t="inlineStr"/>
-      <c r="I56" s="26" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="J56" s="26" t="inlineStr"/>
-      <c r="K56" s="26" t="inlineStr"/>
-      <c r="L56" s="26" t="n">
+      <c r="F56" s="22" t="n"/>
+      <c r="G56" s="22" t="inlineStr"/>
+      <c r="H56" s="22" t="inlineStr"/>
+      <c r="I56" s="25" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="J56" s="25" t="inlineStr"/>
+      <c r="K56" s="25" t="inlineStr"/>
+      <c r="L56" s="25" t="n">
         <v>46.5</v>
       </c>
-      <c r="M56" s="26" t="inlineStr"/>
-      <c r="N56" s="26" t="inlineStr"/>
-      <c r="O56" s="26" t="inlineStr"/>
-      <c r="P56" s="23" t="n"/>
-      <c r="Q56" s="23" t="inlineStr"/>
-      <c r="R56" s="26" t="n">
+      <c r="M56" s="25" t="inlineStr"/>
+      <c r="N56" s="25" t="inlineStr"/>
+      <c r="O56" s="25" t="inlineStr"/>
+      <c r="P56" s="22" t="n"/>
+      <c r="Q56" s="22" t="inlineStr"/>
+      <c r="R56" s="25" t="n">
         <v>45.8</v>
       </c>
-      <c r="S56" s="26" t="inlineStr"/>
-      <c r="T56" s="26" t="inlineStr"/>
-      <c r="U56" s="26" t="n">
+      <c r="S56" s="25" t="inlineStr"/>
+      <c r="T56" s="25" t="inlineStr"/>
+      <c r="U56" s="25" t="n">
         <v>45.4</v>
       </c>
-      <c r="V56" s="26" t="inlineStr"/>
-      <c r="W56" s="26" t="inlineStr"/>
-      <c r="X56" s="23" t="n"/>
-      <c r="Y56" s="23" t="inlineStr"/>
-      <c r="Z56" s="23" t="inlineStr"/>
-      <c r="AA56" s="23" t="inlineStr"/>
-      <c r="AB56" s="23" t="inlineStr"/>
-      <c r="AC56" s="27" t="n">
+      <c r="V56" s="25" t="inlineStr"/>
+      <c r="W56" s="25" t="inlineStr"/>
+      <c r="X56" s="22" t="n"/>
+      <c r="Y56" s="22" t="inlineStr"/>
+      <c r="Z56" s="22" t="inlineStr"/>
+      <c r="AA56" s="22" t="inlineStr"/>
+      <c r="AB56" s="22" t="inlineStr"/>
+      <c r="AC56" s="26" t="n">
         <v>45.2</v>
       </c>
-      <c r="AD56" s="27" t="inlineStr"/>
-      <c r="AE56" s="27" t="inlineStr"/>
+      <c r="AD56" s="26" t="inlineStr"/>
+      <c r="AE56" s="26" t="inlineStr"/>
     </row>
     <row r="57" customHeight="1" ht="15">
       <c r="A57" s="19" t="inlineStr">
@@ -3793,48 +3784,48 @@
       <c r="C57" s="19" t="inlineStr"/>
       <c r="D57" s="19" t="inlineStr"/>
       <c r="E57" s="19" t="inlineStr"/>
-      <c r="F57" s="26" t="n">
+      <c r="F57" s="25" t="n">
         <v>39.0</v>
       </c>
-      <c r="G57" s="26" t="inlineStr"/>
-      <c r="H57" s="26" t="inlineStr"/>
-      <c r="I57" s="26" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="J57" s="26" t="inlineStr"/>
-      <c r="K57" s="26" t="inlineStr"/>
-      <c r="L57" s="26" t="n">
+      <c r="G57" s="25" t="inlineStr"/>
+      <c r="H57" s="25" t="inlineStr"/>
+      <c r="I57" s="25" t="n">
+        <v>44.0</v>
+      </c>
+      <c r="J57" s="25" t="inlineStr"/>
+      <c r="K57" s="25" t="inlineStr"/>
+      <c r="L57" s="25" t="n">
         <v>41.3</v>
       </c>
-      <c r="M57" s="26" t="inlineStr"/>
-      <c r="N57" s="26" t="inlineStr"/>
-      <c r="O57" s="26" t="inlineStr"/>
-      <c r="P57" s="26" t="n">
-        <v>2.2986386599910134</v>
-      </c>
-      <c r="Q57" s="26" t="inlineStr"/>
-      <c r="R57" s="26" t="n">
+      <c r="M57" s="25" t="inlineStr"/>
+      <c r="N57" s="25" t="inlineStr"/>
+      <c r="O57" s="25" t="inlineStr"/>
+      <c r="P57" s="25" t="n">
+        <v>2.25099571330297</v>
+      </c>
+      <c r="Q57" s="25" t="inlineStr"/>
+      <c r="R57" s="25" t="n">
         <v>40.4</v>
       </c>
-      <c r="S57" s="26" t="inlineStr"/>
-      <c r="T57" s="26" t="inlineStr"/>
-      <c r="U57" s="26" t="n">
+      <c r="S57" s="25" t="inlineStr"/>
+      <c r="T57" s="25" t="inlineStr"/>
+      <c r="U57" s="25" t="n">
         <v>40.2</v>
       </c>
-      <c r="V57" s="26" t="inlineStr"/>
-      <c r="W57" s="26" t="inlineStr"/>
-      <c r="X57" s="26" t="n">
-        <v>1.2163040202011715</v>
-      </c>
-      <c r="Y57" s="26" t="inlineStr"/>
-      <c r="Z57" s="26" t="inlineStr"/>
-      <c r="AA57" s="26" t="inlineStr"/>
-      <c r="AB57" s="26" t="inlineStr"/>
-      <c r="AC57" s="27" t="n">
+      <c r="V57" s="25" t="inlineStr"/>
+      <c r="W57" s="25" t="inlineStr"/>
+      <c r="X57" s="25" t="n">
+        <v>1.2047008710417515</v>
+      </c>
+      <c r="Y57" s="25" t="inlineStr"/>
+      <c r="Z57" s="25" t="inlineStr"/>
+      <c r="AA57" s="25" t="inlineStr"/>
+      <c r="AB57" s="25" t="inlineStr"/>
+      <c r="AC57" s="26" t="n">
         <v>40.2</v>
       </c>
-      <c r="AD57" s="27" t="inlineStr"/>
-      <c r="AE57" s="27" t="inlineStr"/>
+      <c r="AD57" s="26" t="inlineStr"/>
+      <c r="AE57" s="26" t="inlineStr"/>
     </row>
     <row r="58" customHeight="1" ht="15">
       <c r="A58" s="19" t="inlineStr">
@@ -3848,42 +3839,42 @@
       <c r="C58" s="19" t="inlineStr"/>
       <c r="D58" s="19" t="inlineStr"/>
       <c r="E58" s="19" t="inlineStr"/>
-      <c r="F58" s="26" t="n"/>
-      <c r="G58" s="26" t="inlineStr"/>
-      <c r="H58" s="26" t="inlineStr"/>
-      <c r="I58" s="26" t="n">
+      <c r="F58" s="25" t="n"/>
+      <c r="G58" s="25" t="inlineStr"/>
+      <c r="H58" s="25" t="inlineStr"/>
+      <c r="I58" s="25" t="n">
         <v>43.1</v>
       </c>
-      <c r="J58" s="26" t="inlineStr"/>
-      <c r="K58" s="26" t="inlineStr"/>
-      <c r="L58" s="26" t="n">
+      <c r="J58" s="25" t="inlineStr"/>
+      <c r="K58" s="25" t="inlineStr"/>
+      <c r="L58" s="25" t="n">
         <v>39.8</v>
       </c>
-      <c r="M58" s="26" t="inlineStr"/>
-      <c r="N58" s="26" t="inlineStr"/>
-      <c r="O58" s="26" t="inlineStr"/>
-      <c r="P58" s="26" t="n"/>
-      <c r="Q58" s="26" t="inlineStr"/>
-      <c r="R58" s="26" t="n">
+      <c r="M58" s="25" t="inlineStr"/>
+      <c r="N58" s="25" t="inlineStr"/>
+      <c r="O58" s="25" t="inlineStr"/>
+      <c r="P58" s="25" t="n"/>
+      <c r="Q58" s="25" t="inlineStr"/>
+      <c r="R58" s="25" t="n">
         <v>39.7</v>
       </c>
-      <c r="S58" s="26" t="inlineStr"/>
-      <c r="T58" s="26" t="inlineStr"/>
-      <c r="U58" s="26" t="n">
+      <c r="S58" s="25" t="inlineStr"/>
+      <c r="T58" s="25" t="inlineStr"/>
+      <c r="U58" s="25" t="n">
         <v>39.7</v>
       </c>
-      <c r="V58" s="26" t="inlineStr"/>
-      <c r="W58" s="26" t="inlineStr"/>
-      <c r="X58" s="26" t="n"/>
-      <c r="Y58" s="26" t="inlineStr"/>
-      <c r="Z58" s="26" t="inlineStr"/>
-      <c r="AA58" s="26" t="inlineStr"/>
-      <c r="AB58" s="26" t="inlineStr"/>
-      <c r="AC58" s="27" t="n">
+      <c r="V58" s="25" t="inlineStr"/>
+      <c r="W58" s="25" t="inlineStr"/>
+      <c r="X58" s="25" t="n"/>
+      <c r="Y58" s="25" t="inlineStr"/>
+      <c r="Z58" s="25" t="inlineStr"/>
+      <c r="AA58" s="25" t="inlineStr"/>
+      <c r="AB58" s="25" t="inlineStr"/>
+      <c r="AC58" s="26" t="n">
         <v>39.9</v>
       </c>
-      <c r="AD58" s="27" t="inlineStr"/>
-      <c r="AE58" s="27" t="inlineStr"/>
+      <c r="AD58" s="26" t="inlineStr"/>
+      <c r="AE58" s="26" t="inlineStr"/>
     </row>
     <row r="59" customHeight="1" ht="15">
       <c r="A59" s="19" t="inlineStr">
@@ -3902,11 +3893,11 @@
       </c>
       <c r="G59" s="20" t="inlineStr"/>
       <c r="H59" s="20" t="inlineStr"/>
-      <c r="I59" s="31" t="n">
+      <c r="I59" s="30" t="n">
         <v>199.0</v>
       </c>
-      <c r="J59" s="31" t="inlineStr"/>
-      <c r="K59" s="31" t="inlineStr"/>
+      <c r="J59" s="30" t="inlineStr"/>
+      <c r="K59" s="30" t="inlineStr"/>
       <c r="L59" s="20" t="n">
         <v>184.0</v>
       </c>
@@ -3934,11 +3925,11 @@
       <c r="Z59" s="20" t="inlineStr"/>
       <c r="AA59" s="20" t="inlineStr"/>
       <c r="AB59" s="20" t="inlineStr"/>
-      <c r="AC59" s="22" t="n">
+      <c r="AC59" s="21" t="n">
         <v>188.0</v>
       </c>
-      <c r="AD59" s="22" t="inlineStr"/>
-      <c r="AE59" s="22" t="inlineStr"/>
+      <c r="AD59" s="21" t="inlineStr"/>
+      <c r="AE59" s="21" t="inlineStr"/>
     </row>
     <row r="60" customHeight="1" ht="15">
       <c r="A60" s="19" t="inlineStr">
@@ -3955,72 +3946,72 @@
       <c r="F60" s="20" t="n"/>
       <c r="G60" s="20" t="inlineStr"/>
       <c r="H60" s="20" t="inlineStr"/>
-      <c r="I60" s="26" t="n">
+      <c r="I60" s="25" t="n">
         <v>0.0</v>
       </c>
-      <c r="J60" s="26" t="inlineStr"/>
-      <c r="K60" s="26" t="inlineStr"/>
-      <c r="L60" s="26" t="n">
+      <c r="J60" s="25" t="inlineStr"/>
+      <c r="K60" s="25" t="inlineStr"/>
+      <c r="L60" s="25" t="n">
         <v>0.0</v>
       </c>
-      <c r="M60" s="26" t="inlineStr"/>
-      <c r="N60" s="26" t="inlineStr"/>
-      <c r="O60" s="26" t="inlineStr"/>
+      <c r="M60" s="25" t="inlineStr"/>
+      <c r="N60" s="25" t="inlineStr"/>
+      <c r="O60" s="25" t="inlineStr"/>
       <c r="P60" s="20" t="n"/>
       <c r="Q60" s="20" t="inlineStr"/>
-      <c r="R60" s="26" t="n">
+      <c r="R60" s="25" t="n">
         <v>0.0</v>
       </c>
-      <c r="S60" s="26" t="inlineStr"/>
-      <c r="T60" s="26" t="inlineStr"/>
-      <c r="U60" s="26" t="n">
+      <c r="S60" s="25" t="inlineStr"/>
+      <c r="T60" s="25" t="inlineStr"/>
+      <c r="U60" s="25" t="n">
         <v>0.0</v>
       </c>
-      <c r="V60" s="26" t="inlineStr"/>
-      <c r="W60" s="26" t="inlineStr"/>
+      <c r="V60" s="25" t="inlineStr"/>
+      <c r="W60" s="25" t="inlineStr"/>
       <c r="X60" s="20" t="n"/>
       <c r="Y60" s="20" t="inlineStr"/>
       <c r="Z60" s="20" t="inlineStr"/>
       <c r="AA60" s="20" t="inlineStr"/>
       <c r="AB60" s="20" t="inlineStr"/>
-      <c r="AC60" s="27" t="n">
+      <c r="AC60" s="26" t="n">
         <v>0.0</v>
       </c>
-      <c r="AD60" s="27" t="inlineStr"/>
-      <c r="AE60" s="27" t="inlineStr"/>
+      <c r="AD60" s="26" t="inlineStr"/>
+      <c r="AE60" s="26" t="inlineStr"/>
     </row>
     <row r="61" customHeight="1" ht="2">
-      <c r="A61" s="30" t="inlineStr"/>
-      <c r="B61" s="30" t="inlineStr"/>
-      <c r="C61" s="30" t="inlineStr"/>
-      <c r="D61" s="30" t="inlineStr"/>
-      <c r="E61" s="30" t="inlineStr"/>
-      <c r="F61" s="30" t="inlineStr"/>
-      <c r="G61" s="30" t="inlineStr"/>
-      <c r="H61" s="30" t="inlineStr"/>
-      <c r="I61" s="30" t="inlineStr"/>
-      <c r="J61" s="30" t="inlineStr"/>
-      <c r="K61" s="30" t="inlineStr"/>
-      <c r="L61" s="30" t="inlineStr"/>
-      <c r="M61" s="30" t="inlineStr"/>
-      <c r="N61" s="30" t="inlineStr"/>
-      <c r="O61" s="30" t="inlineStr"/>
-      <c r="P61" s="30" t="inlineStr"/>
-      <c r="Q61" s="30" t="inlineStr"/>
-      <c r="R61" s="30" t="inlineStr"/>
-      <c r="S61" s="30" t="inlineStr"/>
-      <c r="T61" s="30" t="inlineStr"/>
-      <c r="U61" s="30" t="inlineStr"/>
-      <c r="V61" s="30" t="inlineStr"/>
-      <c r="W61" s="30" t="inlineStr"/>
-      <c r="X61" s="30" t="inlineStr"/>
-      <c r="Y61" s="30" t="inlineStr"/>
-      <c r="Z61" s="30" t="inlineStr"/>
-      <c r="AA61" s="30" t="inlineStr"/>
-      <c r="AB61" s="30" t="inlineStr"/>
-      <c r="AC61" s="30" t="inlineStr"/>
-      <c r="AD61" s="30" t="inlineStr"/>
-      <c r="AE61" s="30" t="inlineStr"/>
+      <c r="A61" s="29" t="inlineStr"/>
+      <c r="B61" s="29" t="inlineStr"/>
+      <c r="C61" s="29" t="inlineStr"/>
+      <c r="D61" s="29" t="inlineStr"/>
+      <c r="E61" s="29" t="inlineStr"/>
+      <c r="F61" s="29" t="inlineStr"/>
+      <c r="G61" s="29" t="inlineStr"/>
+      <c r="H61" s="29" t="inlineStr"/>
+      <c r="I61" s="29" t="inlineStr"/>
+      <c r="J61" s="29" t="inlineStr"/>
+      <c r="K61" s="29" t="inlineStr"/>
+      <c r="L61" s="29" t="inlineStr"/>
+      <c r="M61" s="29" t="inlineStr"/>
+      <c r="N61" s="29" t="inlineStr"/>
+      <c r="O61" s="29" t="inlineStr"/>
+      <c r="P61" s="29" t="inlineStr"/>
+      <c r="Q61" s="29" t="inlineStr"/>
+      <c r="R61" s="29" t="inlineStr"/>
+      <c r="S61" s="29" t="inlineStr"/>
+      <c r="T61" s="29" t="inlineStr"/>
+      <c r="U61" s="29" t="inlineStr"/>
+      <c r="V61" s="29" t="inlineStr"/>
+      <c r="W61" s="29" t="inlineStr"/>
+      <c r="X61" s="29" t="inlineStr"/>
+      <c r="Y61" s="29" t="inlineStr"/>
+      <c r="Z61" s="29" t="inlineStr"/>
+      <c r="AA61" s="29" t="inlineStr"/>
+      <c r="AB61" s="29" t="inlineStr"/>
+      <c r="AC61" s="29" t="inlineStr"/>
+      <c r="AD61" s="29" t="inlineStr"/>
+      <c r="AE61" s="29" t="inlineStr"/>
     </row>
     <row r="62" customHeight="1" ht="21">
       <c r="A62" s="4" t="inlineStr">
@@ -4311,11 +4302,11 @@
       <c r="Z66" s="20" t="inlineStr"/>
       <c r="AA66" s="20" t="inlineStr"/>
       <c r="AB66" s="20" t="inlineStr"/>
-      <c r="AC66" s="22" t="n">
+      <c r="AC66" s="21" t="n">
         <v>1438.0</v>
       </c>
-      <c r="AD66" s="22" t="inlineStr"/>
-      <c r="AE66" s="22" t="inlineStr"/>
+      <c r="AD66" s="21" t="inlineStr"/>
+      <c r="AE66" s="21" t="inlineStr"/>
     </row>
     <row r="67" customHeight="1" ht="15">
       <c r="A67" s="19" t="inlineStr">
@@ -4360,11 +4351,11 @@
       <c r="Z67" s="20" t="inlineStr"/>
       <c r="AA67" s="20" t="inlineStr"/>
       <c r="AB67" s="20" t="inlineStr"/>
-      <c r="AC67" s="22" t="n">
+      <c r="AC67" s="21" t="n">
         <v>0.0</v>
       </c>
-      <c r="AD67" s="22" t="inlineStr"/>
-      <c r="AE67" s="22" t="inlineStr"/>
+      <c r="AD67" s="21" t="inlineStr"/>
+      <c r="AE67" s="21" t="inlineStr"/>
     </row>
     <row r="68" customHeight="1" ht="15">
       <c r="A68" s="19" t="inlineStr">
@@ -4409,44 +4400,44 @@
       <c r="Z68" s="20" t="inlineStr"/>
       <c r="AA68" s="20" t="inlineStr"/>
       <c r="AB68" s="20" t="inlineStr"/>
-      <c r="AC68" s="22" t="n">
+      <c r="AC68" s="21" t="n">
         <v>1438.0</v>
       </c>
-      <c r="AD68" s="22" t="inlineStr"/>
-      <c r="AE68" s="22" t="inlineStr"/>
+      <c r="AD68" s="21" t="inlineStr"/>
+      <c r="AE68" s="21" t="inlineStr"/>
     </row>
     <row r="69" customHeight="1" ht="2">
-      <c r="A69" s="30" t="inlineStr"/>
-      <c r="B69" s="30" t="inlineStr"/>
-      <c r="C69" s="30" t="inlineStr"/>
-      <c r="D69" s="30" t="inlineStr"/>
-      <c r="E69" s="30" t="inlineStr"/>
-      <c r="F69" s="30" t="inlineStr"/>
-      <c r="G69" s="30" t="inlineStr"/>
-      <c r="H69" s="30" t="inlineStr"/>
-      <c r="I69" s="30" t="inlineStr"/>
-      <c r="J69" s="30" t="inlineStr"/>
-      <c r="K69" s="30" t="inlineStr"/>
-      <c r="L69" s="30" t="inlineStr"/>
-      <c r="M69" s="30" t="inlineStr"/>
-      <c r="N69" s="30" t="inlineStr"/>
-      <c r="O69" s="30" t="inlineStr"/>
-      <c r="P69" s="30" t="inlineStr"/>
-      <c r="Q69" s="30" t="inlineStr"/>
-      <c r="R69" s="30" t="inlineStr"/>
-      <c r="S69" s="30" t="inlineStr"/>
-      <c r="T69" s="30" t="inlineStr"/>
-      <c r="U69" s="30" t="inlineStr"/>
-      <c r="V69" s="30" t="inlineStr"/>
-      <c r="W69" s="30" t="inlineStr"/>
-      <c r="X69" s="30" t="inlineStr"/>
-      <c r="Y69" s="30" t="inlineStr"/>
-      <c r="Z69" s="30" t="inlineStr"/>
-      <c r="AA69" s="30" t="inlineStr"/>
-      <c r="AB69" s="30" t="inlineStr"/>
-      <c r="AC69" s="30" t="inlineStr"/>
-      <c r="AD69" s="30" t="inlineStr"/>
-      <c r="AE69" s="30" t="inlineStr"/>
+      <c r="A69" s="29" t="inlineStr"/>
+      <c r="B69" s="29" t="inlineStr"/>
+      <c r="C69" s="29" t="inlineStr"/>
+      <c r="D69" s="29" t="inlineStr"/>
+      <c r="E69" s="29" t="inlineStr"/>
+      <c r="F69" s="29" t="inlineStr"/>
+      <c r="G69" s="29" t="inlineStr"/>
+      <c r="H69" s="29" t="inlineStr"/>
+      <c r="I69" s="29" t="inlineStr"/>
+      <c r="J69" s="29" t="inlineStr"/>
+      <c r="K69" s="29" t="inlineStr"/>
+      <c r="L69" s="29" t="inlineStr"/>
+      <c r="M69" s="29" t="inlineStr"/>
+      <c r="N69" s="29" t="inlineStr"/>
+      <c r="O69" s="29" t="inlineStr"/>
+      <c r="P69" s="29" t="inlineStr"/>
+      <c r="Q69" s="29" t="inlineStr"/>
+      <c r="R69" s="29" t="inlineStr"/>
+      <c r="S69" s="29" t="inlineStr"/>
+      <c r="T69" s="29" t="inlineStr"/>
+      <c r="U69" s="29" t="inlineStr"/>
+      <c r="V69" s="29" t="inlineStr"/>
+      <c r="W69" s="29" t="inlineStr"/>
+      <c r="X69" s="29" t="inlineStr"/>
+      <c r="Y69" s="29" t="inlineStr"/>
+      <c r="Z69" s="29" t="inlineStr"/>
+      <c r="AA69" s="29" t="inlineStr"/>
+      <c r="AB69" s="29" t="inlineStr"/>
+      <c r="AC69" s="29" t="inlineStr"/>
+      <c r="AD69" s="29" t="inlineStr"/>
+      <c r="AE69" s="29" t="inlineStr"/>
     </row>
     <row r="70" customHeight="1" ht="21">
       <c r="A70" s="4" t="inlineStr">
@@ -4709,874 +4700,874 @@
       <c r="F74" s="20" t="n"/>
       <c r="G74" s="20" t="inlineStr"/>
       <c r="H74" s="20" t="inlineStr"/>
-      <c r="I74" s="26" t="n">
+      <c r="I74" s="25" t="n">
         <v>0.0</v>
       </c>
-      <c r="J74" s="26" t="inlineStr"/>
-      <c r="K74" s="26" t="inlineStr"/>
-      <c r="L74" s="26" t="n">
+      <c r="J74" s="25" t="inlineStr"/>
+      <c r="K74" s="25" t="inlineStr"/>
+      <c r="L74" s="25" t="n">
         <v>0.0</v>
       </c>
-      <c r="M74" s="26" t="inlineStr"/>
-      <c r="N74" s="26" t="inlineStr"/>
-      <c r="O74" s="26" t="inlineStr"/>
+      <c r="M74" s="25" t="inlineStr"/>
+      <c r="N74" s="25" t="inlineStr"/>
+      <c r="O74" s="25" t="inlineStr"/>
       <c r="P74" s="20" t="n"/>
       <c r="Q74" s="20" t="inlineStr"/>
-      <c r="R74" s="26" t="n">
+      <c r="R74" s="25" t="n">
         <v>0.0</v>
       </c>
-      <c r="S74" s="26" t="inlineStr"/>
-      <c r="T74" s="26" t="inlineStr"/>
-      <c r="U74" s="26" t="n">
+      <c r="S74" s="25" t="inlineStr"/>
+      <c r="T74" s="25" t="inlineStr"/>
+      <c r="U74" s="25" t="n">
         <v>0.0</v>
       </c>
-      <c r="V74" s="26" t="inlineStr"/>
-      <c r="W74" s="26" t="inlineStr"/>
+      <c r="V74" s="25" t="inlineStr"/>
+      <c r="W74" s="25" t="inlineStr"/>
       <c r="X74" s="20" t="n"/>
       <c r="Y74" s="20" t="inlineStr"/>
       <c r="Z74" s="20" t="inlineStr"/>
       <c r="AA74" s="20" t="inlineStr"/>
       <c r="AB74" s="20" t="inlineStr"/>
-      <c r="AC74" s="27" t="n">
+      <c r="AC74" s="26" t="n">
         <v>0.0</v>
       </c>
-      <c r="AD74" s="27" t="inlineStr"/>
-      <c r="AE74" s="27" t="inlineStr"/>
+      <c r="AD74" s="26" t="inlineStr"/>
+      <c r="AE74" s="26" t="inlineStr"/>
     </row>
     <row r="75" customHeight="1" ht="2">
-      <c r="A75" s="30" t="inlineStr"/>
-      <c r="B75" s="30" t="inlineStr"/>
-      <c r="C75" s="30" t="inlineStr"/>
-      <c r="D75" s="30" t="inlineStr"/>
-      <c r="E75" s="30" t="inlineStr"/>
-      <c r="F75" s="30" t="inlineStr"/>
-      <c r="G75" s="30" t="inlineStr"/>
-      <c r="H75" s="30" t="inlineStr"/>
-      <c r="I75" s="30" t="inlineStr"/>
-      <c r="J75" s="30" t="inlineStr"/>
-      <c r="K75" s="30" t="inlineStr"/>
-      <c r="L75" s="30" t="inlineStr"/>
-      <c r="M75" s="30" t="inlineStr"/>
-      <c r="N75" s="30" t="inlineStr"/>
-      <c r="O75" s="30" t="inlineStr"/>
-      <c r="P75" s="30" t="inlineStr"/>
-      <c r="Q75" s="30" t="inlineStr"/>
-      <c r="R75" s="30" t="inlineStr"/>
-      <c r="S75" s="30" t="inlineStr"/>
-      <c r="T75" s="30" t="inlineStr"/>
-      <c r="U75" s="30" t="inlineStr"/>
-      <c r="V75" s="30" t="inlineStr"/>
-      <c r="W75" s="30" t="inlineStr"/>
-      <c r="X75" s="30" t="inlineStr"/>
-      <c r="Y75" s="30" t="inlineStr"/>
-      <c r="Z75" s="30" t="inlineStr"/>
-      <c r="AA75" s="30" t="inlineStr"/>
-      <c r="AB75" s="30" t="inlineStr"/>
-      <c r="AC75" s="30" t="inlineStr"/>
-      <c r="AD75" s="30" t="inlineStr"/>
-      <c r="AE75" s="30" t="inlineStr"/>
+      <c r="A75" s="29" t="inlineStr"/>
+      <c r="B75" s="29" t="inlineStr"/>
+      <c r="C75" s="29" t="inlineStr"/>
+      <c r="D75" s="29" t="inlineStr"/>
+      <c r="E75" s="29" t="inlineStr"/>
+      <c r="F75" s="29" t="inlineStr"/>
+      <c r="G75" s="29" t="inlineStr"/>
+      <c r="H75" s="29" t="inlineStr"/>
+      <c r="I75" s="29" t="inlineStr"/>
+      <c r="J75" s="29" t="inlineStr"/>
+      <c r="K75" s="29" t="inlineStr"/>
+      <c r="L75" s="29" t="inlineStr"/>
+      <c r="M75" s="29" t="inlineStr"/>
+      <c r="N75" s="29" t="inlineStr"/>
+      <c r="O75" s="29" t="inlineStr"/>
+      <c r="P75" s="29" t="inlineStr"/>
+      <c r="Q75" s="29" t="inlineStr"/>
+      <c r="R75" s="29" t="inlineStr"/>
+      <c r="S75" s="29" t="inlineStr"/>
+      <c r="T75" s="29" t="inlineStr"/>
+      <c r="U75" s="29" t="inlineStr"/>
+      <c r="V75" s="29" t="inlineStr"/>
+      <c r="W75" s="29" t="inlineStr"/>
+      <c r="X75" s="29" t="inlineStr"/>
+      <c r="Y75" s="29" t="inlineStr"/>
+      <c r="Z75" s="29" t="inlineStr"/>
+      <c r="AA75" s="29" t="inlineStr"/>
+      <c r="AB75" s="29" t="inlineStr"/>
+      <c r="AC75" s="29" t="inlineStr"/>
+      <c r="AD75" s="29" t="inlineStr"/>
+      <c r="AE75" s="29" t="inlineStr"/>
     </row>
     <row r="76" customHeight="1" ht="21">
-      <c r="A76" s="36" t="inlineStr">
+      <c r="A76" s="35" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Farings prognose</t>
           </r>
         </is>
       </c>
-      <c r="B76" s="36" t="inlineStr"/>
-      <c r="C76" s="36" t="inlineStr"/>
-      <c r="D76" s="36" t="inlineStr"/>
-      <c r="E76" s="36" t="inlineStr"/>
-      <c r="F76" s="36" t="inlineStr"/>
-      <c r="G76" s="36" t="inlineStr"/>
-      <c r="H76" s="36" t="inlineStr"/>
-      <c r="I76" s="36" t="inlineStr"/>
-      <c r="J76" s="36" t="inlineStr"/>
-      <c r="K76" s="36" t="inlineStr"/>
-      <c r="L76" s="36" t="inlineStr"/>
-      <c r="M76" s="36" t="inlineStr"/>
-      <c r="N76" s="36" t="inlineStr"/>
-      <c r="O76" s="36" t="inlineStr"/>
-      <c r="P76" s="36" t="inlineStr"/>
-      <c r="Q76" s="36" t="inlineStr"/>
-      <c r="R76" s="36" t="inlineStr"/>
-      <c r="S76" s="36" t="inlineStr"/>
-      <c r="T76" s="36" t="inlineStr"/>
-      <c r="U76" s="36" t="inlineStr"/>
-      <c r="V76" s="36" t="inlineStr"/>
-      <c r="W76" s="36" t="inlineStr"/>
-      <c r="X76" s="36" t="inlineStr"/>
-      <c r="Y76" s="36" t="inlineStr"/>
-      <c r="Z76" s="36" t="inlineStr"/>
-      <c r="AA76" s="36" t="inlineStr"/>
-      <c r="AB76" s="36" t="inlineStr"/>
-      <c r="AC76" s="36" t="inlineStr"/>
-      <c r="AD76" s="36" t="inlineStr"/>
-      <c r="AE76" s="36" t="inlineStr"/>
+      <c r="B76" s="35" t="inlineStr"/>
+      <c r="C76" s="35" t="inlineStr"/>
+      <c r="D76" s="35" t="inlineStr"/>
+      <c r="E76" s="35" t="inlineStr"/>
+      <c r="F76" s="35" t="inlineStr"/>
+      <c r="G76" s="35" t="inlineStr"/>
+      <c r="H76" s="35" t="inlineStr"/>
+      <c r="I76" s="35" t="inlineStr"/>
+      <c r="J76" s="35" t="inlineStr"/>
+      <c r="K76" s="35" t="inlineStr"/>
+      <c r="L76" s="35" t="inlineStr"/>
+      <c r="M76" s="35" t="inlineStr"/>
+      <c r="N76" s="35" t="inlineStr"/>
+      <c r="O76" s="35" t="inlineStr"/>
+      <c r="P76" s="35" t="inlineStr"/>
+      <c r="Q76" s="35" t="inlineStr"/>
+      <c r="R76" s="35" t="inlineStr"/>
+      <c r="S76" s="35" t="inlineStr"/>
+      <c r="T76" s="35" t="inlineStr"/>
+      <c r="U76" s="35" t="inlineStr"/>
+      <c r="V76" s="35" t="inlineStr"/>
+      <c r="W76" s="35" t="inlineStr"/>
+      <c r="X76" s="35" t="inlineStr"/>
+      <c r="Y76" s="35" t="inlineStr"/>
+      <c r="Z76" s="35" t="inlineStr"/>
+      <c r="AA76" s="35" t="inlineStr"/>
+      <c r="AB76" s="35" t="inlineStr"/>
+      <c r="AC76" s="35" t="inlineStr"/>
+      <c r="AD76" s="35" t="inlineStr"/>
+      <c r="AE76" s="35" t="inlineStr"/>
     </row>
     <row r="77" customHeight="1" ht="20">
-      <c r="A77" s="37" t="inlineStr">
+      <c r="A77" s="36" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Uge</t>
           </r>
         </is>
       </c>
-      <c r="B77" s="37" t="inlineStr"/>
-      <c r="C77" s="38" t="n">
+      <c r="B77" s="36" t="inlineStr"/>
+      <c r="C77" s="37" t="n">
         <v>15.0</v>
       </c>
-      <c r="D77" s="38" t="n">
+      <c r="D77" s="37" t="n">
         <v>14.0</v>
       </c>
-      <c r="E77" s="38" t="n">
+      <c r="E77" s="37" t="n">
         <v>13.0</v>
       </c>
-      <c r="F77" s="38" t="inlineStr"/>
-      <c r="G77" s="38" t="n">
+      <c r="F77" s="37" t="inlineStr"/>
+      <c r="G77" s="37" t="n">
         <v>12.0</v>
       </c>
-      <c r="H77" s="38" t="n">
+      <c r="H77" s="37" t="n">
         <v>11.0</v>
       </c>
-      <c r="I77" s="38" t="inlineStr"/>
-      <c r="J77" s="38" t="n">
+      <c r="I77" s="37" t="inlineStr"/>
+      <c r="J77" s="37" t="n">
         <v>10.0</v>
       </c>
-      <c r="K77" s="38" t="n">
+      <c r="K77" s="37" t="n">
         <v>9.0</v>
       </c>
-      <c r="L77" s="38" t="inlineStr"/>
-      <c r="M77" s="38" t="n">
+      <c r="L77" s="37" t="inlineStr"/>
+      <c r="M77" s="37" t="n">
         <v>8.0</v>
       </c>
-      <c r="N77" s="38" t="inlineStr"/>
-      <c r="O77" s="38" t="n">
+      <c r="N77" s="37" t="inlineStr"/>
+      <c r="O77" s="37" t="n">
         <v>7.0</v>
       </c>
-      <c r="P77" s="38" t="inlineStr"/>
-      <c r="Q77" s="38" t="n">
+      <c r="P77" s="37" t="inlineStr"/>
+      <c r="Q77" s="37" t="n">
         <v>6.0</v>
       </c>
-      <c r="R77" s="38" t="inlineStr"/>
-      <c r="S77" s="38" t="n">
+      <c r="R77" s="37" t="inlineStr"/>
+      <c r="S77" s="37" t="n">
         <v>5.0</v>
       </c>
-      <c r="T77" s="38" t="n">
+      <c r="T77" s="37" t="n">
         <v>4.0</v>
       </c>
-      <c r="U77" s="38" t="inlineStr"/>
-      <c r="V77" s="38" t="n">
+      <c r="U77" s="37" t="inlineStr"/>
+      <c r="V77" s="37" t="n">
         <v>3.0</v>
       </c>
-      <c r="W77" s="38" t="n">
+      <c r="W77" s="37" t="n">
         <v>2.0</v>
       </c>
-      <c r="X77" s="38" t="inlineStr"/>
-      <c r="Y77" s="38" t="inlineStr"/>
-      <c r="Z77" s="38" t="inlineStr"/>
-      <c r="AA77" s="38" t="n">
+      <c r="X77" s="37" t="inlineStr"/>
+      <c r="Y77" s="37" t="inlineStr"/>
+      <c r="Z77" s="37" t="inlineStr"/>
+      <c r="AA77" s="37" t="n">
         <v>1.0</v>
       </c>
-      <c r="AB77" s="38" t="n">
+      <c r="AB77" s="37" t="n">
         <v>52.0</v>
       </c>
-      <c r="AC77" s="38" t="inlineStr"/>
-      <c r="AD77" s="38" t="n">
+      <c r="AC77" s="37" t="inlineStr"/>
+      <c r="AD77" s="37" t="n">
         <v>51.0</v>
       </c>
-      <c r="AE77" s="38" t="inlineStr"/>
+      <c r="AE77" s="37" t="inlineStr"/>
     </row>
     <row r="78" customHeight="1" ht="20">
-      <c r="A78" s="39" t="inlineStr">
+      <c r="A78" s="38" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Løbninger</t>
           </r>
         </is>
       </c>
-      <c r="B78" s="39" t="inlineStr"/>
-      <c r="C78" s="40" t="n">
-        <v>84.0</v>
-      </c>
-      <c r="D78" s="40" t="n">
+      <c r="B78" s="38" t="inlineStr"/>
+      <c r="C78" s="39" t="n">
+        <v>90.0</v>
+      </c>
+      <c r="D78" s="39" t="n">
         <v>89.0</v>
       </c>
-      <c r="E78" s="40" t="n">
+      <c r="E78" s="39" t="n">
         <v>89.0</v>
       </c>
-      <c r="F78" s="40" t="inlineStr"/>
-      <c r="G78" s="40" t="n">
+      <c r="F78" s="39" t="inlineStr"/>
+      <c r="G78" s="39" t="n">
         <v>91.0</v>
       </c>
-      <c r="H78" s="40" t="n">
+      <c r="H78" s="39" t="n">
         <v>91.0</v>
       </c>
-      <c r="I78" s="40" t="inlineStr"/>
-      <c r="J78" s="40" t="n">
+      <c r="I78" s="39" t="inlineStr"/>
+      <c r="J78" s="39" t="n">
         <v>88.0</v>
       </c>
-      <c r="K78" s="40" t="n">
+      <c r="K78" s="39" t="n">
         <v>90.0</v>
       </c>
-      <c r="L78" s="40" t="inlineStr"/>
-      <c r="M78" s="40" t="n">
+      <c r="L78" s="39" t="inlineStr"/>
+      <c r="M78" s="39" t="n">
         <v>88.0</v>
       </c>
-      <c r="N78" s="40" t="inlineStr"/>
-      <c r="O78" s="40" t="n">
+      <c r="N78" s="39" t="inlineStr"/>
+      <c r="O78" s="39" t="n">
         <v>89.0</v>
       </c>
-      <c r="P78" s="40" t="inlineStr"/>
-      <c r="Q78" s="40" t="n">
+      <c r="P78" s="39" t="inlineStr"/>
+      <c r="Q78" s="39" t="n">
         <v>88.0</v>
       </c>
-      <c r="R78" s="40" t="inlineStr"/>
-      <c r="S78" s="40" t="n">
+      <c r="R78" s="39" t="inlineStr"/>
+      <c r="S78" s="39" t="n">
         <v>87.0</v>
       </c>
-      <c r="T78" s="40" t="n">
+      <c r="T78" s="39" t="n">
         <v>89.0</v>
       </c>
-      <c r="U78" s="40" t="inlineStr"/>
-      <c r="V78" s="40" t="n">
+      <c r="U78" s="39" t="inlineStr"/>
+      <c r="V78" s="39" t="n">
         <v>90.0</v>
       </c>
-      <c r="W78" s="40" t="n">
+      <c r="W78" s="39" t="n">
         <v>90.0</v>
       </c>
-      <c r="X78" s="40" t="inlineStr"/>
-      <c r="Y78" s="40" t="inlineStr"/>
-      <c r="Z78" s="40" t="inlineStr"/>
-      <c r="AA78" s="40" t="n">
+      <c r="X78" s="39" t="inlineStr"/>
+      <c r="Y78" s="39" t="inlineStr"/>
+      <c r="Z78" s="39" t="inlineStr"/>
+      <c r="AA78" s="39" t="n">
         <v>89.0</v>
       </c>
-      <c r="AB78" s="40" t="n">
+      <c r="AB78" s="39" t="n">
         <v>89.0</v>
       </c>
-      <c r="AC78" s="40" t="inlineStr"/>
-      <c r="AD78" s="40" t="n">
+      <c r="AC78" s="39" t="inlineStr"/>
+      <c r="AD78" s="39" t="n">
         <v>91.0</v>
       </c>
-      <c r="AE78" s="40" t="inlineStr"/>
+      <c r="AE78" s="39" t="inlineStr"/>
     </row>
     <row r="79" customHeight="1" ht="20">
-      <c r="A79" s="39" t="inlineStr">
+      <c r="A79" s="38" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Scannet ikke drægtig</t>
           </r>
         </is>
       </c>
-      <c r="B79" s="39" t="inlineStr"/>
-      <c r="C79" s="40" t="n">
+      <c r="B79" s="38" t="inlineStr"/>
+      <c r="C79" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="D79" s="40" t="n">
+      <c r="D79" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="E79" s="40" t="n">
+      <c r="E79" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="F79" s="40" t="inlineStr"/>
-      <c r="G79" s="40" t="n">
+      <c r="F79" s="39" t="inlineStr"/>
+      <c r="G79" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="H79" s="40" t="n">
+      <c r="H79" s="39" t="n">
         <v>1.0</v>
       </c>
-      <c r="I79" s="40" t="inlineStr"/>
-      <c r="J79" s="40" t="n">
+      <c r="I79" s="39" t="inlineStr"/>
+      <c r="J79" s="39" t="n">
         <v>2.0</v>
       </c>
-      <c r="K79" s="40" t="n">
+      <c r="K79" s="39" t="n">
         <v>1.0</v>
       </c>
-      <c r="L79" s="40" t="inlineStr"/>
-      <c r="M79" s="40" t="n">
+      <c r="L79" s="39" t="inlineStr"/>
+      <c r="M79" s="39" t="n">
         <v>1.0</v>
       </c>
-      <c r="N79" s="40" t="inlineStr"/>
-      <c r="O79" s="40" t="n">
+      <c r="N79" s="39" t="inlineStr"/>
+      <c r="O79" s="39" t="n">
         <v>4.0</v>
       </c>
-      <c r="P79" s="40" t="inlineStr"/>
-      <c r="Q79" s="40" t="n">
+      <c r="P79" s="39" t="inlineStr"/>
+      <c r="Q79" s="39" t="n">
         <v>2.0</v>
       </c>
-      <c r="R79" s="40" t="inlineStr"/>
-      <c r="S79" s="40" t="n">
+      <c r="R79" s="39" t="inlineStr"/>
+      <c r="S79" s="39" t="n">
         <v>2.0</v>
       </c>
-      <c r="T79" s="40" t="n">
+      <c r="T79" s="39" t="n">
         <v>1.0</v>
       </c>
-      <c r="U79" s="40" t="inlineStr"/>
-      <c r="V79" s="40" t="n">
+      <c r="U79" s="39" t="inlineStr"/>
+      <c r="V79" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="W79" s="40" t="n">
+      <c r="W79" s="39" t="n">
         <v>3.0</v>
       </c>
-      <c r="X79" s="40" t="inlineStr"/>
-      <c r="Y79" s="40" t="inlineStr"/>
-      <c r="Z79" s="40" t="inlineStr"/>
-      <c r="AA79" s="40" t="n">
+      <c r="X79" s="39" t="inlineStr"/>
+      <c r="Y79" s="39" t="inlineStr"/>
+      <c r="Z79" s="39" t="inlineStr"/>
+      <c r="AA79" s="39" t="n">
         <v>1.0</v>
       </c>
-      <c r="AB79" s="40" t="n">
+      <c r="AB79" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="AC79" s="40" t="inlineStr"/>
-      <c r="AD79" s="40" t="n">
+      <c r="AC79" s="39" t="inlineStr"/>
+      <c r="AD79" s="39" t="n">
         <v>1.0</v>
       </c>
-      <c r="AE79" s="40" t="inlineStr"/>
+      <c r="AE79" s="39" t="inlineStr"/>
     </row>
     <row r="80" customHeight="1" ht="20">
-      <c r="A80" s="39" t="inlineStr">
+      <c r="A80" s="38" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Kastninger</t>
           </r>
         </is>
       </c>
-      <c r="B80" s="39" t="inlineStr"/>
-      <c r="C80" s="40" t="n">
+      <c r="B80" s="38" t="inlineStr"/>
+      <c r="C80" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="D80" s="40" t="n">
+      <c r="D80" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="E80" s="40" t="n">
+      <c r="E80" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="F80" s="40" t="inlineStr"/>
-      <c r="G80" s="40" t="n">
+      <c r="F80" s="39" t="inlineStr"/>
+      <c r="G80" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="H80" s="40" t="n">
+      <c r="H80" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="I80" s="40" t="inlineStr"/>
-      <c r="J80" s="40" t="n">
+      <c r="I80" s="39" t="inlineStr"/>
+      <c r="J80" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="K80" s="40" t="n">
+      <c r="K80" s="39" t="n">
         <v>1.0</v>
       </c>
-      <c r="L80" s="40" t="inlineStr"/>
-      <c r="M80" s="40" t="n">
+      <c r="L80" s="39" t="inlineStr"/>
+      <c r="M80" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="N80" s="40" t="inlineStr"/>
-      <c r="O80" s="40" t="n">
+      <c r="N80" s="39" t="inlineStr"/>
+      <c r="O80" s="39" t="n">
         <v>2.0</v>
       </c>
-      <c r="P80" s="40" t="inlineStr"/>
-      <c r="Q80" s="40" t="n">
+      <c r="P80" s="39" t="inlineStr"/>
+      <c r="Q80" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="R80" s="40" t="inlineStr"/>
-      <c r="S80" s="40" t="n">
+      <c r="R80" s="39" t="inlineStr"/>
+      <c r="S80" s="39" t="n">
         <v>1.0</v>
       </c>
-      <c r="T80" s="40" t="n">
+      <c r="T80" s="39" t="n">
         <v>1.0</v>
       </c>
-      <c r="U80" s="40" t="inlineStr"/>
-      <c r="V80" s="40" t="n">
+      <c r="U80" s="39" t="inlineStr"/>
+      <c r="V80" s="39" t="n">
         <v>1.0</v>
       </c>
-      <c r="W80" s="40" t="n">
+      <c r="W80" s="39" t="n">
         <v>1.0</v>
       </c>
-      <c r="X80" s="40" t="inlineStr"/>
-      <c r="Y80" s="40" t="inlineStr"/>
-      <c r="Z80" s="40" t="inlineStr"/>
-      <c r="AA80" s="40" t="n">
+      <c r="X80" s="39" t="inlineStr"/>
+      <c r="Y80" s="39" t="inlineStr"/>
+      <c r="Z80" s="39" t="inlineStr"/>
+      <c r="AA80" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="AB80" s="40" t="n">
+      <c r="AB80" s="39" t="n">
         <v>1.0</v>
       </c>
-      <c r="AC80" s="40" t="inlineStr"/>
-      <c r="AD80" s="40" t="n">
+      <c r="AC80" s="39" t="inlineStr"/>
+      <c r="AD80" s="39" t="n">
         <v>1.0</v>
       </c>
-      <c r="AE80" s="40" t="inlineStr"/>
+      <c r="AE80" s="39" t="inlineStr"/>
     </row>
     <row r="81" customHeight="1" ht="20">
-      <c r="A81" s="39" t="inlineStr">
+      <c r="A81" s="38" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Omløbninger</t>
           </r>
         </is>
       </c>
-      <c r="B81" s="39" t="inlineStr"/>
-      <c r="C81" s="40" t="n">
+      <c r="B81" s="38" t="inlineStr"/>
+      <c r="C81" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="D81" s="40" t="n">
+      <c r="D81" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="E81" s="40" t="n">
+      <c r="E81" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="F81" s="40" t="inlineStr"/>
-      <c r="G81" s="40" t="n">
+      <c r="F81" s="39" t="inlineStr"/>
+      <c r="G81" s="39" t="n">
         <v>1.0</v>
       </c>
-      <c r="H81" s="40" t="n">
+      <c r="H81" s="39" t="n">
         <v>1.0</v>
       </c>
-      <c r="I81" s="40" t="inlineStr"/>
-      <c r="J81" s="40" t="n">
+      <c r="I81" s="39" t="inlineStr"/>
+      <c r="J81" s="39" t="n">
         <v>1.0</v>
       </c>
-      <c r="K81" s="40" t="n">
+      <c r="K81" s="39" t="n">
         <v>2.0</v>
       </c>
-      <c r="L81" s="40" t="inlineStr"/>
-      <c r="M81" s="40" t="n">
+      <c r="L81" s="39" t="inlineStr"/>
+      <c r="M81" s="39" t="n">
         <v>1.0</v>
       </c>
-      <c r="N81" s="40" t="inlineStr"/>
-      <c r="O81" s="40" t="n">
+      <c r="N81" s="39" t="inlineStr"/>
+      <c r="O81" s="39" t="n">
         <v>1.0</v>
       </c>
-      <c r="P81" s="40" t="inlineStr"/>
-      <c r="Q81" s="40" t="n">
+      <c r="P81" s="39" t="inlineStr"/>
+      <c r="Q81" s="39" t="n">
         <v>3.0</v>
       </c>
-      <c r="R81" s="40" t="inlineStr"/>
-      <c r="S81" s="40" t="n">
+      <c r="R81" s="39" t="inlineStr"/>
+      <c r="S81" s="39" t="n">
         <v>2.0</v>
       </c>
-      <c r="T81" s="40" t="n">
+      <c r="T81" s="39" t="n">
         <v>2.0</v>
       </c>
-      <c r="U81" s="40" t="inlineStr"/>
-      <c r="V81" s="40" t="n">
+      <c r="U81" s="39" t="inlineStr"/>
+      <c r="V81" s="39" t="n">
         <v>3.0</v>
       </c>
-      <c r="W81" s="40" t="n">
+      <c r="W81" s="39" t="n">
         <v>3.0</v>
       </c>
-      <c r="X81" s="40" t="inlineStr"/>
-      <c r="Y81" s="40" t="inlineStr"/>
-      <c r="Z81" s="40" t="inlineStr"/>
-      <c r="AA81" s="40" t="n">
+      <c r="X81" s="39" t="inlineStr"/>
+      <c r="Y81" s="39" t="inlineStr"/>
+      <c r="Z81" s="39" t="inlineStr"/>
+      <c r="AA81" s="39" t="n">
         <v>1.0</v>
       </c>
-      <c r="AB81" s="40" t="n">
+      <c r="AB81" s="39" t="n">
         <v>3.0</v>
       </c>
-      <c r="AC81" s="40" t="inlineStr"/>
-      <c r="AD81" s="40" t="n">
+      <c r="AC81" s="39" t="inlineStr"/>
+      <c r="AD81" s="39" t="n">
         <v>2.0</v>
       </c>
-      <c r="AE81" s="40" t="inlineStr"/>
+      <c r="AE81" s="39" t="inlineStr"/>
     </row>
     <row r="82" customHeight="1" ht="20">
-      <c r="A82" s="39" t="inlineStr">
+      <c r="A82" s="38" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Solgt til slagt</t>
           </r>
         </is>
       </c>
-      <c r="B82" s="39" t="inlineStr"/>
-      <c r="C82" s="40" t="n">
+      <c r="B82" s="38" t="inlineStr"/>
+      <c r="C82" s="39" t="n">
         <v>1.0</v>
       </c>
-      <c r="D82" s="40" t="n">
+      <c r="D82" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="E82" s="40" t="n">
+      <c r="E82" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="F82" s="40" t="inlineStr"/>
-      <c r="G82" s="40" t="n">
+      <c r="F82" s="39" t="inlineStr"/>
+      <c r="G82" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="H82" s="40" t="n">
+      <c r="H82" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="I82" s="40" t="inlineStr"/>
-      <c r="J82" s="40" t="n">
+      <c r="I82" s="39" t="inlineStr"/>
+      <c r="J82" s="39" t="n">
         <v>2.0</v>
       </c>
-      <c r="K82" s="40" t="n">
+      <c r="K82" s="39" t="n">
         <v>1.0</v>
       </c>
-      <c r="L82" s="40" t="inlineStr"/>
-      <c r="M82" s="40" t="n">
+      <c r="L82" s="39" t="inlineStr"/>
+      <c r="M82" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="N82" s="40" t="inlineStr"/>
-      <c r="O82" s="40" t="n">
+      <c r="N82" s="39" t="inlineStr"/>
+      <c r="O82" s="39" t="n">
         <v>3.0</v>
       </c>
-      <c r="P82" s="40" t="inlineStr"/>
-      <c r="Q82" s="40" t="n">
+      <c r="P82" s="39" t="inlineStr"/>
+      <c r="Q82" s="39" t="n">
         <v>1.0</v>
       </c>
-      <c r="R82" s="40" t="inlineStr"/>
-      <c r="S82" s="40" t="n">
+      <c r="R82" s="39" t="inlineStr"/>
+      <c r="S82" s="39" t="n">
         <v>2.0</v>
       </c>
-      <c r="T82" s="40" t="n">
+      <c r="T82" s="39" t="n">
         <v>1.0</v>
       </c>
-      <c r="U82" s="40" t="inlineStr"/>
-      <c r="V82" s="40" t="n">
+      <c r="U82" s="39" t="inlineStr"/>
+      <c r="V82" s="39" t="n">
         <v>1.0</v>
       </c>
-      <c r="W82" s="40" t="n">
+      <c r="W82" s="39" t="n">
         <v>2.0</v>
       </c>
-      <c r="X82" s="40" t="inlineStr"/>
-      <c r="Y82" s="40" t="inlineStr"/>
-      <c r="Z82" s="40" t="inlineStr"/>
-      <c r="AA82" s="40" t="n">
+      <c r="X82" s="39" t="inlineStr"/>
+      <c r="Y82" s="39" t="inlineStr"/>
+      <c r="Z82" s="39" t="inlineStr"/>
+      <c r="AA82" s="39" t="n">
         <v>5.0</v>
       </c>
-      <c r="AB82" s="40" t="n">
+      <c r="AB82" s="39" t="n">
         <v>1.0</v>
       </c>
-      <c r="AC82" s="40" t="inlineStr"/>
-      <c r="AD82" s="40" t="n">
+      <c r="AC82" s="39" t="inlineStr"/>
+      <c r="AD82" s="39" t="n">
         <v>1.0</v>
       </c>
-      <c r="AE82" s="40" t="inlineStr"/>
+      <c r="AE82" s="39" t="inlineStr"/>
     </row>
     <row r="83" customHeight="1" ht="20">
-      <c r="A83" s="39" t="inlineStr">
+      <c r="A83" s="38" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Død</t>
           </r>
         </is>
       </c>
-      <c r="B83" s="39" t="inlineStr"/>
-      <c r="C83" s="40" t="n">
+      <c r="B83" s="38" t="inlineStr"/>
+      <c r="C83" s="39" t="n">
         <v>1.0</v>
       </c>
-      <c r="D83" s="40" t="n">
+      <c r="D83" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="E83" s="40" t="n">
+      <c r="E83" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="F83" s="40" t="inlineStr"/>
-      <c r="G83" s="40" t="n">
+      <c r="F83" s="39" t="inlineStr"/>
+      <c r="G83" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="H83" s="40" t="n">
+      <c r="H83" s="39" t="n">
         <v>1.0</v>
       </c>
-      <c r="I83" s="40" t="inlineStr"/>
-      <c r="J83" s="40" t="n">
+      <c r="I83" s="39" t="inlineStr"/>
+      <c r="J83" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="K83" s="40" t="n">
+      <c r="K83" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="L83" s="40" t="inlineStr"/>
-      <c r="M83" s="40" t="n">
+      <c r="L83" s="39" t="inlineStr"/>
+      <c r="M83" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="N83" s="40" t="inlineStr"/>
-      <c r="O83" s="40" t="n">
+      <c r="N83" s="39" t="inlineStr"/>
+      <c r="O83" s="39" t="n">
         <v>2.0</v>
       </c>
-      <c r="P83" s="40" t="inlineStr"/>
-      <c r="Q83" s="40" t="n">
+      <c r="P83" s="39" t="inlineStr"/>
+      <c r="Q83" s="39" t="n">
         <v>2.0</v>
       </c>
-      <c r="R83" s="40" t="inlineStr"/>
-      <c r="S83" s="40" t="n">
+      <c r="R83" s="39" t="inlineStr"/>
+      <c r="S83" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="T83" s="40" t="n">
+      <c r="T83" s="39" t="n">
         <v>2.0</v>
       </c>
-      <c r="U83" s="40" t="inlineStr"/>
-      <c r="V83" s="40" t="n">
+      <c r="U83" s="39" t="inlineStr"/>
+      <c r="V83" s="39" t="n">
         <v>2.0</v>
       </c>
-      <c r="W83" s="40" t="n">
+      <c r="W83" s="39" t="n">
         <v>2.0</v>
       </c>
-      <c r="X83" s="40" t="inlineStr"/>
-      <c r="Y83" s="40" t="inlineStr"/>
-      <c r="Z83" s="40" t="inlineStr"/>
-      <c r="AA83" s="40" t="n">
+      <c r="X83" s="39" t="inlineStr"/>
+      <c r="Y83" s="39" t="inlineStr"/>
+      <c r="Z83" s="39" t="inlineStr"/>
+      <c r="AA83" s="39" t="n">
         <v>2.0</v>
       </c>
-      <c r="AB83" s="40" t="n">
+      <c r="AB83" s="39" t="n">
         <v>3.0</v>
       </c>
-      <c r="AC83" s="40" t="inlineStr"/>
-      <c r="AD83" s="40" t="n">
+      <c r="AC83" s="39" t="inlineStr"/>
+      <c r="AD83" s="39" t="n">
         <v>5.0</v>
       </c>
-      <c r="AE83" s="40" t="inlineStr"/>
+      <c r="AE83" s="39" t="inlineStr"/>
     </row>
     <row r="84" customHeight="1" ht="20">
-      <c r="A84" s="39" t="inlineStr">
+      <c r="A84" s="38" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Drægt.solgt</t>
           </r>
         </is>
       </c>
-      <c r="B84" s="39" t="inlineStr"/>
-      <c r="C84" s="40" t="n">
+      <c r="B84" s="38" t="inlineStr"/>
+      <c r="C84" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="D84" s="40" t="n">
+      <c r="D84" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="E84" s="40" t="n">
+      <c r="E84" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="F84" s="40" t="inlineStr"/>
-      <c r="G84" s="40" t="n">
+      <c r="F84" s="39" t="inlineStr"/>
+      <c r="G84" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="H84" s="40" t="n">
+      <c r="H84" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="I84" s="40" t="inlineStr"/>
-      <c r="J84" s="40" t="n">
+      <c r="I84" s="39" t="inlineStr"/>
+      <c r="J84" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="K84" s="40" t="n">
+      <c r="K84" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="L84" s="40" t="inlineStr"/>
-      <c r="M84" s="40" t="n">
+      <c r="L84" s="39" t="inlineStr"/>
+      <c r="M84" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="N84" s="40" t="inlineStr"/>
-      <c r="O84" s="40" t="n">
+      <c r="N84" s="39" t="inlineStr"/>
+      <c r="O84" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="P84" s="40" t="inlineStr"/>
-      <c r="Q84" s="40" t="n">
+      <c r="P84" s="39" t="inlineStr"/>
+      <c r="Q84" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="R84" s="40" t="inlineStr"/>
-      <c r="S84" s="40" t="n">
+      <c r="R84" s="39" t="inlineStr"/>
+      <c r="S84" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="T84" s="40" t="n">
+      <c r="T84" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="U84" s="40" t="inlineStr"/>
-      <c r="V84" s="40" t="n">
+      <c r="U84" s="39" t="inlineStr"/>
+      <c r="V84" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="W84" s="40" t="n">
+      <c r="W84" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="X84" s="40" t="inlineStr"/>
-      <c r="Y84" s="40" t="inlineStr"/>
-      <c r="Z84" s="40" t="inlineStr"/>
-      <c r="AA84" s="40" t="n">
+      <c r="X84" s="39" t="inlineStr"/>
+      <c r="Y84" s="39" t="inlineStr"/>
+      <c r="Z84" s="39" t="inlineStr"/>
+      <c r="AA84" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="AB84" s="40" t="n">
+      <c r="AB84" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="AC84" s="40" t="inlineStr"/>
-      <c r="AD84" s="40" t="n">
+      <c r="AC84" s="39" t="inlineStr"/>
+      <c r="AD84" s="39" t="n">
         <v>0.0</v>
       </c>
-      <c r="AE84" s="40" t="inlineStr"/>
+      <c r="AE84" s="39" t="inlineStr"/>
     </row>
     <row r="85" customHeight="1" ht="20">
-      <c r="A85" s="39" t="inlineStr">
+      <c r="A85" s="38" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Far.prognose</t>
           </r>
         </is>
       </c>
-      <c r="B85" s="39" t="inlineStr"/>
-      <c r="C85" s="40" t="n">
+      <c r="B85" s="38" t="inlineStr"/>
+      <c r="C85" s="39" t="n">
+        <v>88.0</v>
+      </c>
+      <c r="D85" s="39" t="n">
+        <v>89.0</v>
+      </c>
+      <c r="E85" s="39" t="n">
+        <v>89.0</v>
+      </c>
+      <c r="F85" s="39" t="inlineStr"/>
+      <c r="G85" s="39" t="n">
+        <v>90.0</v>
+      </c>
+      <c r="H85" s="39" t="n">
+        <v>88.0</v>
+      </c>
+      <c r="I85" s="39" t="inlineStr"/>
+      <c r="J85" s="39" t="n">
+        <v>83.0</v>
+      </c>
+      <c r="K85" s="39" t="n">
+        <v>85.0</v>
+      </c>
+      <c r="L85" s="39" t="inlineStr"/>
+      <c r="M85" s="39" t="n">
+        <v>86.0</v>
+      </c>
+      <c r="N85" s="39" t="inlineStr"/>
+      <c r="O85" s="39" t="n">
+        <v>77.0</v>
+      </c>
+      <c r="P85" s="39" t="inlineStr"/>
+      <c r="Q85" s="39" t="n">
+        <v>80.0</v>
+      </c>
+      <c r="R85" s="39" t="inlineStr"/>
+      <c r="S85" s="39" t="n">
+        <v>80.0</v>
+      </c>
+      <c r="T85" s="39" t="n">
         <v>82.0</v>
       </c>
-      <c r="D85" s="40" t="n">
-        <v>89.0</v>
-      </c>
-      <c r="E85" s="40" t="n">
-        <v>89.0</v>
-      </c>
-      <c r="F85" s="40" t="inlineStr"/>
-      <c r="G85" s="40" t="n">
-        <v>90.0</v>
-      </c>
-      <c r="H85" s="40" t="n">
-        <v>88.0</v>
-      </c>
-      <c r="I85" s="40" t="inlineStr"/>
-      <c r="J85" s="40" t="n">
+      <c r="U85" s="39" t="inlineStr"/>
+      <c r="V85" s="39" t="n">
         <v>83.0</v>
       </c>
-      <c r="K85" s="40" t="n">
-        <v>85.0</v>
-      </c>
-      <c r="L85" s="40" t="inlineStr"/>
-      <c r="M85" s="40" t="n">
-        <v>86.0</v>
-      </c>
-      <c r="N85" s="40" t="inlineStr"/>
-      <c r="O85" s="40" t="n">
-        <v>77.0</v>
-      </c>
-      <c r="P85" s="40" t="inlineStr"/>
-      <c r="Q85" s="40" t="n">
+      <c r="W85" s="39" t="n">
+        <v>79.0</v>
+      </c>
+      <c r="X85" s="39" t="inlineStr"/>
+      <c r="Y85" s="39" t="inlineStr"/>
+      <c r="Z85" s="39" t="inlineStr"/>
+      <c r="AA85" s="39" t="n">
         <v>80.0</v>
       </c>
-      <c r="R85" s="40" t="inlineStr"/>
-      <c r="S85" s="40" t="n">
-        <v>80.0</v>
-      </c>
-      <c r="T85" s="40" t="n">
-        <v>82.0</v>
-      </c>
-      <c r="U85" s="40" t="inlineStr"/>
-      <c r="V85" s="40" t="n">
-        <v>83.0</v>
-      </c>
-      <c r="W85" s="40" t="n">
-        <v>79.0</v>
-      </c>
-      <c r="X85" s="40" t="inlineStr"/>
-      <c r="Y85" s="40" t="inlineStr"/>
-      <c r="Z85" s="40" t="inlineStr"/>
-      <c r="AA85" s="40" t="n">
-        <v>80.0</v>
-      </c>
-      <c r="AB85" s="40" t="n">
+      <c r="AB85" s="39" t="n">
         <v>81.0</v>
       </c>
-      <c r="AC85" s="40" t="inlineStr"/>
-      <c r="AD85" s="40" t="n">
+      <c r="AC85" s="39" t="inlineStr"/>
+      <c r="AD85" s="39" t="n">
         <v>81.0</v>
       </c>
-      <c r="AE85" s="40" t="inlineStr"/>
+      <c r="AE85" s="39" t="inlineStr"/>
     </row>
     <row r="86" customHeight="1" ht="20">
-      <c r="A86" s="41" t="inlineStr">
+      <c r="A86" s="40" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Far.rate</t>
           </r>
         </is>
       </c>
-      <c r="B86" s="41" t="inlineStr"/>
-      <c r="C86" s="42" t="n">
-        <v>0.9761904761904762</v>
-      </c>
-      <c r="D86" s="42" t="n">
+      <c r="B86" s="40" t="inlineStr"/>
+      <c r="C86" s="41" t="n">
+        <v>0.9777777777777777</v>
+      </c>
+      <c r="D86" s="41" t="n">
         <v>1.0</v>
       </c>
-      <c r="E86" s="42" t="n">
+      <c r="E86" s="41" t="n">
         <v>1.0</v>
       </c>
-      <c r="F86" s="42" t="inlineStr"/>
-      <c r="G86" s="42" t="n">
+      <c r="F86" s="41" t="inlineStr"/>
+      <c r="G86" s="41" t="n">
         <v>0.989010989010989</v>
       </c>
-      <c r="H86" s="42" t="n">
+      <c r="H86" s="41" t="n">
         <v>0.967032967032967</v>
       </c>
-      <c r="I86" s="42" t="inlineStr"/>
-      <c r="J86" s="42" t="n">
+      <c r="I86" s="41" t="inlineStr"/>
+      <c r="J86" s="41" t="n">
         <v>0.9431818181818182</v>
       </c>
-      <c r="K86" s="42" t="n">
+      <c r="K86" s="41" t="n">
         <v>0.9444444444444444</v>
       </c>
-      <c r="L86" s="42" t="inlineStr"/>
-      <c r="M86" s="42" t="n">
+      <c r="L86" s="41" t="inlineStr"/>
+      <c r="M86" s="41" t="n">
         <v>0.9772727272727273</v>
       </c>
-      <c r="N86" s="42" t="inlineStr"/>
-      <c r="O86" s="42" t="n">
+      <c r="N86" s="41" t="inlineStr"/>
+      <c r="O86" s="41" t="n">
         <v>0.8651685393258427</v>
       </c>
-      <c r="P86" s="42" t="inlineStr"/>
-      <c r="Q86" s="42" t="n">
+      <c r="P86" s="41" t="inlineStr"/>
+      <c r="Q86" s="41" t="n">
         <v>0.9090909090909091</v>
       </c>
-      <c r="R86" s="42" t="inlineStr"/>
-      <c r="S86" s="42" t="n">
+      <c r="R86" s="41" t="inlineStr"/>
+      <c r="S86" s="41" t="n">
         <v>0.9195402298850575</v>
       </c>
-      <c r="T86" s="42" t="n">
+      <c r="T86" s="41" t="n">
         <v>0.9213483146067416</v>
       </c>
-      <c r="U86" s="42" t="inlineStr"/>
-      <c r="V86" s="42" t="n">
+      <c r="U86" s="41" t="inlineStr"/>
+      <c r="V86" s="41" t="n">
         <v>0.9222222222222223</v>
       </c>
-      <c r="W86" s="42" t="n">
+      <c r="W86" s="41" t="n">
         <v>0.8777777777777778</v>
       </c>
-      <c r="X86" s="42" t="inlineStr"/>
-      <c r="Y86" s="42" t="inlineStr"/>
-      <c r="Z86" s="42" t="inlineStr"/>
-      <c r="AA86" s="42" t="n">
+      <c r="X86" s="41" t="inlineStr"/>
+      <c r="Y86" s="41" t="inlineStr"/>
+      <c r="Z86" s="41" t="inlineStr"/>
+      <c r="AA86" s="41" t="n">
         <v>0.898876404494382</v>
       </c>
-      <c r="AB86" s="42" t="n">
+      <c r="AB86" s="41" t="n">
         <v>0.9101123595505618</v>
       </c>
-      <c r="AC86" s="42" t="inlineStr"/>
-      <c r="AD86" s="42" t="n">
+      <c r="AC86" s="41" t="inlineStr"/>
+      <c r="AD86" s="41" t="n">
         <v>0.8901098901098901</v>
       </c>
-      <c r="AE86" s="42" t="inlineStr"/>
+      <c r="AE86" s="41" t="inlineStr"/>
     </row>
     <row r="87" customHeight="1" ht="1">
-      <c r="A87" s="43" t="inlineStr"/>
-      <c r="B87" s="43" t="inlineStr"/>
-      <c r="C87" s="43" t="inlineStr"/>
-      <c r="D87" s="43" t="inlineStr"/>
-      <c r="E87" s="43" t="inlineStr"/>
-      <c r="F87" s="43" t="inlineStr"/>
-      <c r="G87" s="43" t="inlineStr"/>
-      <c r="H87" s="43" t="inlineStr"/>
-      <c r="I87" s="43" t="inlineStr"/>
-      <c r="J87" s="43" t="inlineStr"/>
-      <c r="K87" s="43" t="inlineStr"/>
-      <c r="L87" s="43" t="inlineStr"/>
-      <c r="M87" s="43" t="inlineStr"/>
-      <c r="N87" s="43" t="inlineStr"/>
-      <c r="O87" s="43" t="inlineStr"/>
-      <c r="P87" s="43" t="inlineStr"/>
-      <c r="Q87" s="43" t="inlineStr"/>
-      <c r="R87" s="43" t="inlineStr"/>
-      <c r="S87" s="43" t="inlineStr"/>
-      <c r="T87" s="43" t="inlineStr"/>
-      <c r="U87" s="43" t="inlineStr"/>
-      <c r="V87" s="43" t="inlineStr"/>
-      <c r="W87" s="43" t="inlineStr"/>
-      <c r="X87" s="43" t="inlineStr"/>
-      <c r="Y87" s="43" t="inlineStr"/>
-      <c r="Z87" s="43" t="inlineStr"/>
-      <c r="AA87" s="43" t="inlineStr"/>
-      <c r="AB87" s="43" t="inlineStr"/>
-      <c r="AC87" s="43" t="inlineStr"/>
-      <c r="AD87" s="43" t="inlineStr"/>
-      <c r="AE87" s="43" t="inlineStr"/>
+      <c r="A87" s="42" t="inlineStr"/>
+      <c r="B87" s="42" t="inlineStr"/>
+      <c r="C87" s="42" t="inlineStr"/>
+      <c r="D87" s="42" t="inlineStr"/>
+      <c r="E87" s="42" t="inlineStr"/>
+      <c r="F87" s="42" t="inlineStr"/>
+      <c r="G87" s="42" t="inlineStr"/>
+      <c r="H87" s="42" t="inlineStr"/>
+      <c r="I87" s="42" t="inlineStr"/>
+      <c r="J87" s="42" t="inlineStr"/>
+      <c r="K87" s="42" t="inlineStr"/>
+      <c r="L87" s="42" t="inlineStr"/>
+      <c r="M87" s="42" t="inlineStr"/>
+      <c r="N87" s="42" t="inlineStr"/>
+      <c r="O87" s="42" t="inlineStr"/>
+      <c r="P87" s="42" t="inlineStr"/>
+      <c r="Q87" s="42" t="inlineStr"/>
+      <c r="R87" s="42" t="inlineStr"/>
+      <c r="S87" s="42" t="inlineStr"/>
+      <c r="T87" s="42" t="inlineStr"/>
+      <c r="U87" s="42" t="inlineStr"/>
+      <c r="V87" s="42" t="inlineStr"/>
+      <c r="W87" s="42" t="inlineStr"/>
+      <c r="X87" s="42" t="inlineStr"/>
+      <c r="Y87" s="42" t="inlineStr"/>
+      <c r="Z87" s="42" t="inlineStr"/>
+      <c r="AA87" s="42" t="inlineStr"/>
+      <c r="AB87" s="42" t="inlineStr"/>
+      <c r="AC87" s="42" t="inlineStr"/>
+      <c r="AD87" s="42" t="inlineStr"/>
+      <c r="AE87" s="42" t="inlineStr"/>
     </row>
     <row r="88" customHeight="1" ht="6">
       <c r="A88" s="11" t="inlineStr"/>
@@ -5612,7 +5603,7 @@
       <c r="AE88" s="11" t="inlineStr"/>
     </row>
     <row r="89" customHeight="1" ht="14">
-      <c r="A89" s="44" t="n">
+      <c r="A89" s="43" t="n">
         <v>1.0</v>
       </c>
       <c r="B89" s="11" t="inlineStr"/>
@@ -5627,23 +5618,23 @@
       <c r="K89" s="11" t="inlineStr"/>
       <c r="L89" s="11" t="inlineStr"/>
       <c r="M89" s="11" t="inlineStr"/>
-      <c r="N89" s="45" t="inlineStr">
+      <c r="N89" s="44" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Produceret af</t>
           </r>
         </is>
       </c>
-      <c r="O89" s="45" t="inlineStr"/>
-      <c r="P89" s="45" t="inlineStr"/>
-      <c r="Q89" s="45" t="inlineStr"/>
-      <c r="R89" s="45" t="inlineStr"/>
-      <c r="S89" s="45" t="inlineStr"/>
-      <c r="T89" s="45" t="inlineStr"/>
-      <c r="U89" s="45" t="inlineStr"/>
-      <c r="V89" s="45" t="inlineStr"/>
-      <c r="W89" s="45" t="inlineStr"/>
-      <c r="X89" s="45" t="inlineStr"/>
+      <c r="O89" s="44" t="inlineStr"/>
+      <c r="P89" s="44" t="inlineStr"/>
+      <c r="Q89" s="44" t="inlineStr"/>
+      <c r="R89" s="44" t="inlineStr"/>
+      <c r="S89" s="44" t="inlineStr"/>
+      <c r="T89" s="44" t="inlineStr"/>
+      <c r="U89" s="44" t="inlineStr"/>
+      <c r="V89" s="44" t="inlineStr"/>
+      <c r="W89" s="44" t="inlineStr"/>
+      <c r="X89" s="44" t="inlineStr"/>
       <c r="Y89" s="11" t="inlineStr"/>
       <c r="Z89" s="12" t="inlineStr"/>
       <c r="AA89" s="12" t="inlineStr"/>
